--- a/research/traditional_assets/database/data/poland/poland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08970954743829634</v>
+        <v>0.0895755492981636</v>
       </c>
       <c r="C2">
-        <v>692.1735321587689</v>
+        <v>686.8312720780115</v>
       </c>
       <c r="D2">
-        <v>596.7735321587689</v>
+        <v>598.6002720780115</v>
       </c>
       <c r="E2">
-        <v>-489</v>
+        <v>-481.831</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.169</v>
       </c>
       <c r="G2">
         <v>95.40000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3606006999999999</v>
       </c>
       <c r="N2">
-        <v>84.19999999999999</v>
+        <v>83.83939929999998</v>
       </c>
       <c r="O2">
-        <v>15.998</v>
+        <v>15.929485867</v>
       </c>
       <c r="P2">
-        <v>68.202</v>
+        <v>67.90991343299999</v>
       </c>
       <c r="Q2">
-        <v>137.002</v>
+        <v>136.709913433</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08970954743829634</v>
+        <v>0.09006880737188241</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8107987535790236</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>233.4992694135092</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0895755492981636</v>
+        <v>0.08944155115803082</v>
       </c>
       <c r="C3">
-        <v>686.8312720780115</v>
+        <v>681.5002297356341</v>
       </c>
       <c r="D3">
-        <v>598.6002720780115</v>
+        <v>600.4382297356341</v>
       </c>
       <c r="E3">
-        <v>-481.831</v>
+        <v>-474.662</v>
       </c>
       <c r="F3">
-        <v>7.169</v>
+        <v>14.338</v>
       </c>
       <c r="G3">
         <v>95.40000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M3">
-        <v>0.3606006999999999</v>
+        <v>0.7212013999999999</v>
       </c>
       <c r="N3">
-        <v>83.83939929999998</v>
+        <v>83.47879859999999</v>
       </c>
       <c r="O3">
-        <v>15.929485867</v>
+        <v>15.860971734</v>
       </c>
       <c r="P3">
-        <v>67.90991343299999</v>
+        <v>67.61782686599999</v>
       </c>
       <c r="Q3">
-        <v>136.709913433</v>
+        <v>136.417826866</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09006880737188241</v>
+        <v>0.09043539914084778</v>
       </c>
       <c r="T3">
-        <v>0.8107987535790236</v>
+        <v>0.8175130105693359</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>233.4992694135092</v>
+        <v>116.7496347067546</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08944155115803082</v>
+        <v>0.08930755301789807</v>
       </c>
       <c r="C4">
-        <v>681.5002297356341</v>
+        <v>676.1805087795756</v>
       </c>
       <c r="D4">
-        <v>600.4382297356341</v>
+        <v>602.2875087795755</v>
       </c>
       <c r="E4">
-        <v>-474.662</v>
+        <v>-467.493</v>
       </c>
       <c r="F4">
-        <v>14.338</v>
+        <v>21.507</v>
       </c>
       <c r="G4">
         <v>95.40000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M4">
-        <v>0.7212013999999999</v>
+        <v>1.0818021</v>
       </c>
       <c r="N4">
-        <v>83.47879859999999</v>
+        <v>83.11819789999998</v>
       </c>
       <c r="O4">
-        <v>15.860971734</v>
+        <v>15.792457601</v>
       </c>
       <c r="P4">
-        <v>67.61782686599999</v>
+        <v>67.32574029899999</v>
       </c>
       <c r="Q4">
-        <v>136.417826866</v>
+        <v>136.125740299</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09043539914084778</v>
+        <v>0.0908095495029877</v>
       </c>
       <c r="T4">
-        <v>0.8175130105693359</v>
+        <v>0.8243657058481082</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>116.7496347067546</v>
+        <v>77.83308980450306</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08930755301789807</v>
+        <v>0.08917355487776529</v>
       </c>
       <c r="C5">
-        <v>676.1805087795756</v>
+        <v>670.8722141386154</v>
       </c>
       <c r="D5">
-        <v>602.2875087795755</v>
+        <v>604.1482141386155</v>
       </c>
       <c r="E5">
-        <v>-467.493</v>
+        <v>-460.324</v>
       </c>
       <c r="F5">
-        <v>21.507</v>
+        <v>28.676</v>
       </c>
       <c r="G5">
         <v>95.40000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M5">
-        <v>1.0818021</v>
+        <v>1.4424028</v>
       </c>
       <c r="N5">
-        <v>83.11819789999998</v>
+        <v>82.75759719999999</v>
       </c>
       <c r="O5">
-        <v>15.792457601</v>
+        <v>15.723943468</v>
       </c>
       <c r="P5">
-        <v>67.32574029899999</v>
+        <v>67.03365373199999</v>
       </c>
       <c r="Q5">
-        <v>136.125740299</v>
+        <v>135.833653732</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0908095495029877</v>
+        <v>0.09119149466433885</v>
       </c>
       <c r="T5">
-        <v>0.8243657058481082</v>
+        <v>0.8313611656118549</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.83308980450306</v>
+        <v>58.3748173533773</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08917355487776529</v>
+        <v>0.08903955673763254</v>
       </c>
       <c r="C6">
-        <v>670.8722141386154</v>
+        <v>665.5754520422162</v>
       </c>
       <c r="D6">
-        <v>604.1482141386155</v>
+        <v>606.0204520422162</v>
       </c>
       <c r="E6">
-        <v>-460.324</v>
+        <v>-453.155</v>
       </c>
       <c r="F6">
-        <v>28.676</v>
+        <v>35.845</v>
       </c>
       <c r="G6">
         <v>95.40000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M6">
-        <v>1.4424028</v>
+        <v>1.8030035</v>
       </c>
       <c r="N6">
-        <v>82.75759719999999</v>
+        <v>82.39699649999999</v>
       </c>
       <c r="O6">
-        <v>15.723943468</v>
+        <v>15.655429335</v>
       </c>
       <c r="P6">
-        <v>67.03365373199999</v>
+        <v>66.74156716499999</v>
       </c>
       <c r="Q6">
-        <v>135.833653732</v>
+        <v>135.541567165</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09119149466433885</v>
+        <v>0.09158148077645531</v>
       </c>
       <c r="T6">
-        <v>0.8313611656118549</v>
+        <v>0.8385038982127332</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.3748173533773</v>
+        <v>46.69985388270184</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08903955673763254</v>
+        <v>0.08890555859749977</v>
       </c>
       <c r="C7">
-        <v>665.5754520422162</v>
+        <v>660.2903300407442</v>
       </c>
       <c r="D7">
-        <v>606.0204520422162</v>
+        <v>607.9043300407442</v>
       </c>
       <c r="E7">
-        <v>-453.155</v>
+        <v>-445.986</v>
       </c>
       <c r="F7">
-        <v>35.845</v>
+        <v>43.014</v>
       </c>
       <c r="G7">
         <v>95.40000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M7">
-        <v>1.8030035</v>
+        <v>2.1636042</v>
       </c>
       <c r="N7">
-        <v>82.39699649999999</v>
+        <v>82.03639579999999</v>
       </c>
       <c r="O7">
-        <v>15.655429335</v>
+        <v>15.586915202</v>
       </c>
       <c r="P7">
-        <v>66.74156716499999</v>
+        <v>66.44948059799999</v>
       </c>
       <c r="Q7">
-        <v>135.541567165</v>
+        <v>135.249480598</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09158148077645531</v>
+        <v>0.09197976446542529</v>
       </c>
       <c r="T7">
-        <v>0.8385038982127332</v>
+        <v>0.8457986038476727</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.69985388270184</v>
+        <v>38.91654490225153</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08890555859749977</v>
+        <v>0.08877156045736702</v>
       </c>
       <c r="C8">
-        <v>660.2903300407442</v>
+        <v>655.0169570260597</v>
       </c>
       <c r="D8">
-        <v>607.9043300407442</v>
+        <v>609.7999570260597</v>
       </c>
       <c r="E8">
-        <v>-445.986</v>
+        <v>-438.817</v>
       </c>
       <c r="F8">
-        <v>43.014</v>
+        <v>50.18299999999999</v>
       </c>
       <c r="G8">
         <v>95.40000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M8">
-        <v>2.1636042</v>
+        <v>2.5242049</v>
       </c>
       <c r="N8">
-        <v>82.03639579999999</v>
+        <v>81.67579509999999</v>
       </c>
       <c r="O8">
-        <v>15.586915202</v>
+        <v>15.518401069</v>
       </c>
       <c r="P8">
-        <v>66.44948059799999</v>
+        <v>66.157394031</v>
       </c>
       <c r="Q8">
-        <v>135.249480598</v>
+        <v>134.957394031</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09197976446542529</v>
+        <v>0.09238661339501829</v>
       </c>
       <c r="T8">
-        <v>0.8457986038476727</v>
+        <v>0.853250184872611</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.91654490225154</v>
+        <v>33.35703848764417</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.088771560457367</v>
+        <v>0.08863756231723426</v>
       </c>
       <c r="C9">
-        <v>655.0169570260599</v>
+        <v>649.7554432525029</v>
       </c>
       <c r="D9">
-        <v>609.7999570260599</v>
+        <v>611.7074432525029</v>
       </c>
       <c r="E9">
-        <v>-438.817</v>
+        <v>-431.648</v>
       </c>
       <c r="F9">
-        <v>50.183</v>
+        <v>57.352</v>
       </c>
       <c r="G9">
         <v>95.40000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M9">
-        <v>2.5242049</v>
+        <v>2.8848056</v>
       </c>
       <c r="N9">
-        <v>81.67579509999999</v>
+        <v>81.3151944</v>
       </c>
       <c r="O9">
-        <v>15.518401069</v>
+        <v>15.449886936</v>
       </c>
       <c r="P9">
-        <v>66.157394031</v>
+        <v>65.865307464</v>
       </c>
       <c r="Q9">
-        <v>134.957394031</v>
+        <v>134.665307464</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09238661339501829</v>
+        <v>0.09280230686655896</v>
       </c>
       <c r="T9">
-        <v>0.853250184872611</v>
+        <v>0.8608637567893958</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.35703848764416</v>
+        <v>29.18740867668865</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08863756231723426</v>
+        <v>0.08850356417710148</v>
       </c>
       <c r="C10">
-        <v>649.7554432525029</v>
+        <v>644.5059003582676</v>
       </c>
       <c r="D10">
-        <v>611.7074432525029</v>
+        <v>613.6269003582676</v>
       </c>
       <c r="E10">
-        <v>-431.648</v>
+        <v>-424.479</v>
       </c>
       <c r="F10">
-        <v>57.352</v>
+        <v>64.521</v>
       </c>
       <c r="G10">
         <v>95.40000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M10">
-        <v>2.8848056</v>
+        <v>3.2454063</v>
       </c>
       <c r="N10">
-        <v>81.3151944</v>
+        <v>80.95459369999999</v>
       </c>
       <c r="O10">
-        <v>15.449886936</v>
+        <v>15.381372803</v>
       </c>
       <c r="P10">
-        <v>65.865307464</v>
+        <v>65.573220897</v>
       </c>
       <c r="Q10">
-        <v>134.665307464</v>
+        <v>134.373220897</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09280230686655896</v>
+        <v>0.09322713645835327</v>
       </c>
       <c r="T10">
-        <v>0.8608637567893958</v>
+        <v>0.8686446599570986</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.18740867668865</v>
+        <v>25.94436326816768</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08850356417710148</v>
+        <v>0.08836956603696873</v>
       </c>
       <c r="C11">
-        <v>644.5059003582676</v>
+        <v>639.2684413871807</v>
       </c>
       <c r="D11">
-        <v>613.6269003582676</v>
+        <v>615.5584413871807</v>
       </c>
       <c r="E11">
-        <v>-424.479</v>
+        <v>-417.31</v>
       </c>
       <c r="F11">
-        <v>64.521</v>
+        <v>71.69</v>
       </c>
       <c r="G11">
         <v>95.40000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M11">
-        <v>3.2454063</v>
+        <v>3.606007</v>
       </c>
       <c r="N11">
-        <v>80.95459369999999</v>
+        <v>80.59399299999998</v>
       </c>
       <c r="O11">
-        <v>15.381372803</v>
+        <v>15.31285867</v>
       </c>
       <c r="P11">
-        <v>65.573220897</v>
+        <v>65.28113432999999</v>
       </c>
       <c r="Q11">
-        <v>134.373220897</v>
+        <v>134.08113433</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09322713645835327</v>
+        <v>0.09366140670774303</v>
       </c>
       <c r="T11">
-        <v>0.8686446599570986</v>
+        <v>0.8765984720840841</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.94436326816768</v>
+        <v>23.34992694135092</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08836956603696873</v>
+        <v>0.08823556789683595</v>
       </c>
       <c r="C12">
-        <v>639.2684413871807</v>
+        <v>634.043180810898</v>
       </c>
       <c r="D12">
-        <v>615.5584413871807</v>
+        <v>617.502180810898</v>
       </c>
       <c r="E12">
-        <v>-417.31</v>
+        <v>-410.141</v>
       </c>
       <c r="F12">
-        <v>71.69</v>
+        <v>78.85899999999999</v>
       </c>
       <c r="G12">
         <v>95.40000000000001</v>
@@ -2271,28 +2271,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M12">
-        <v>3.606007</v>
+        <v>3.9666077</v>
       </c>
       <c r="N12">
-        <v>80.59399299999998</v>
+        <v>80.23339229999999</v>
       </c>
       <c r="O12">
-        <v>15.31285867</v>
+        <v>15.244344537</v>
       </c>
       <c r="P12">
-        <v>65.28113432999999</v>
+        <v>64.98904776299999</v>
       </c>
       <c r="Q12">
-        <v>134.08113433</v>
+        <v>133.789047763</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09366140670774303</v>
+        <v>0.09410543583914152</v>
       </c>
       <c r="T12">
-        <v>0.8765984720840841</v>
+        <v>0.8847310215622375</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.34992694135092</v>
+        <v>21.22720631031902</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08823556789683595</v>
+        <v>0.08810156975670319</v>
       </c>
       <c r="C13">
-        <v>634.043180810898</v>
+        <v>628.8302345515153</v>
       </c>
       <c r="D13">
-        <v>617.502180810898</v>
+        <v>619.4582345515154</v>
       </c>
       <c r="E13">
-        <v>-410.141</v>
+        <v>-402.972</v>
       </c>
       <c r="F13">
-        <v>78.85899999999999</v>
+        <v>86.02799999999999</v>
       </c>
       <c r="G13">
         <v>95.40000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M13">
-        <v>3.9666077</v>
+        <v>4.327208399999999</v>
       </c>
       <c r="N13">
-        <v>80.23339229999999</v>
+        <v>79.87279159999999</v>
       </c>
       <c r="O13">
-        <v>15.244344537</v>
+        <v>15.175830404</v>
       </c>
       <c r="P13">
-        <v>64.98904776299999</v>
+        <v>64.69696119599999</v>
       </c>
       <c r="Q13">
-        <v>133.789047763</v>
+        <v>133.496961196</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09410543583914152</v>
+        <v>0.09455955654170817</v>
       </c>
       <c r="T13">
-        <v>0.8847310215622375</v>
+        <v>0.893048401710349</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.22720631031902</v>
+        <v>19.45827245112577</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08810156975670319</v>
+        <v>0.08796757161657044</v>
       </c>
       <c r="C14">
-        <v>628.8302345515153</v>
+        <v>623.6297200046165</v>
       </c>
       <c r="D14">
-        <v>619.4582345515154</v>
+        <v>621.4267200046165</v>
       </c>
       <c r="E14">
-        <v>-402.972</v>
+        <v>-395.803</v>
       </c>
       <c r="F14">
-        <v>86.02799999999999</v>
+        <v>93.197</v>
       </c>
       <c r="G14">
         <v>95.40000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M14">
-        <v>4.327208399999999</v>
+        <v>4.6878091</v>
       </c>
       <c r="N14">
-        <v>79.87279159999999</v>
+        <v>79.51219089999999</v>
       </c>
       <c r="O14">
-        <v>15.175830404</v>
+        <v>15.107316271</v>
       </c>
       <c r="P14">
-        <v>64.69696119599999</v>
+        <v>64.40487462899999</v>
       </c>
       <c r="Q14">
-        <v>133.496961196</v>
+        <v>133.204874629</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09455955654170817</v>
+        <v>0.09502411680065567</v>
       </c>
       <c r="T14">
-        <v>0.893048401710349</v>
+        <v>0.9015569859997967</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.45827245112577</v>
+        <v>17.96148226257763</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08796757161657044</v>
+        <v>0.08783357347643768</v>
       </c>
       <c r="C15">
-        <v>623.6297200046165</v>
+        <v>618.4417560627594</v>
       </c>
       <c r="D15">
-        <v>621.4267200046165</v>
+        <v>623.4077560627594</v>
       </c>
       <c r="E15">
-        <v>-395.803</v>
+        <v>-388.634</v>
       </c>
       <c r="F15">
-        <v>93.197</v>
+        <v>100.366</v>
       </c>
       <c r="G15">
         <v>95.40000000000001</v>
@@ -2517,28 +2517,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M15">
-        <v>4.6878091</v>
+        <v>5.0484098</v>
       </c>
       <c r="N15">
-        <v>79.51219089999999</v>
+        <v>79.15159019999999</v>
       </c>
       <c r="O15">
-        <v>15.107316271</v>
+        <v>15.038802138</v>
       </c>
       <c r="P15">
-        <v>64.40487462899999</v>
+        <v>64.11278806199999</v>
       </c>
       <c r="Q15">
-        <v>133.204874629</v>
+        <v>132.912788062</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09502411680065567</v>
+        <v>0.09549948078655543</v>
       </c>
       <c r="T15">
-        <v>0.9015569859997967</v>
+        <v>0.9102634443424872</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.96148226257763</v>
+        <v>16.67851924382208</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08783357347643768</v>
+        <v>0.08769957533630492</v>
       </c>
       <c r="C16">
-        <v>618.4417560627594</v>
+        <v>613.2664631394125</v>
       </c>
       <c r="D16">
-        <v>623.4077560627594</v>
+        <v>625.4014631394125</v>
       </c>
       <c r="E16">
-        <v>-388.634</v>
+        <v>-381.465</v>
       </c>
       <c r="F16">
-        <v>100.366</v>
+        <v>107.535</v>
       </c>
       <c r="G16">
         <v>95.40000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M16">
-        <v>5.0484098</v>
+        <v>5.4090105</v>
       </c>
       <c r="N16">
-        <v>79.15159019999999</v>
+        <v>78.79098949999999</v>
       </c>
       <c r="O16">
-        <v>15.038802138</v>
+        <v>14.970288005</v>
       </c>
       <c r="P16">
-        <v>64.11278806199999</v>
+        <v>63.82070149499999</v>
       </c>
       <c r="Q16">
-        <v>132.912788062</v>
+        <v>132.620701495</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09549948078655543</v>
+        <v>0.09598602980741755</v>
       </c>
       <c r="T16">
-        <v>0.9102634443424872</v>
+        <v>0.9191747605285351</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.67851924382208</v>
+        <v>15.56661796090061</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08769957533630492</v>
+        <v>0.08756557719617215</v>
       </c>
       <c r="C17">
-        <v>613.2664631394125</v>
+        <v>608.1039631933534</v>
       </c>
       <c r="D17">
-        <v>625.4014631394125</v>
+        <v>627.4079631933533</v>
       </c>
       <c r="E17">
-        <v>-381.465</v>
+        <v>-374.296</v>
       </c>
       <c r="F17">
-        <v>107.535</v>
+        <v>114.704</v>
       </c>
       <c r="G17">
         <v>95.40000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M17">
-        <v>5.4090105</v>
+        <v>5.769611199999999</v>
       </c>
       <c r="N17">
-        <v>78.79098949999999</v>
+        <v>78.43038879999999</v>
       </c>
       <c r="O17">
-        <v>14.970288005</v>
+        <v>14.901773872</v>
       </c>
       <c r="P17">
-        <v>63.82070149499999</v>
+        <v>63.52861492799999</v>
       </c>
       <c r="Q17">
-        <v>132.620701495</v>
+        <v>132.328614928</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09598602980741755</v>
+        <v>0.09648416332877637</v>
       </c>
       <c r="T17">
-        <v>0.9191747605285351</v>
+        <v>0.9282982509094888</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.56661796090061</v>
+        <v>14.59370433834432</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08756557719617215</v>
+        <v>0.08743157905603939</v>
       </c>
       <c r="C18">
-        <v>608.1039631933534</v>
+        <v>602.9543797535378</v>
       </c>
       <c r="D18">
-        <v>627.4079631933533</v>
+        <v>629.4273797535378</v>
       </c>
       <c r="E18">
-        <v>-374.296</v>
+        <v>-367.127</v>
       </c>
       <c r="F18">
-        <v>114.704</v>
+        <v>121.873</v>
       </c>
       <c r="G18">
         <v>95.40000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M18">
-        <v>5.769611199999999</v>
+        <v>6.1302119</v>
       </c>
       <c r="N18">
-        <v>78.43038879999999</v>
+        <v>78.06978809999998</v>
       </c>
       <c r="O18">
-        <v>14.901773872</v>
+        <v>14.833259739</v>
       </c>
       <c r="P18">
-        <v>63.52861492799999</v>
+        <v>63.23652836099998</v>
       </c>
       <c r="Q18">
-        <v>132.328614928</v>
+        <v>132.036528361</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09648416332877637</v>
+        <v>0.09699430006751733</v>
       </c>
       <c r="T18">
-        <v>0.9282982509094888</v>
+        <v>0.9376415844321523</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.59370433834432</v>
+        <v>13.73525114197113</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08743157905603939</v>
+        <v>0.08729758091590661</v>
       </c>
       <c r="C19">
-        <v>602.9543797535378</v>
+        <v>597.817837944451</v>
       </c>
       <c r="D19">
-        <v>629.4273797535378</v>
+        <v>631.459837944451</v>
       </c>
       <c r="E19">
-        <v>-367.127</v>
+        <v>-359.958</v>
       </c>
       <c r="F19">
-        <v>121.873</v>
+        <v>129.042</v>
       </c>
       <c r="G19">
         <v>95.40000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M19">
-        <v>6.1302119</v>
+        <v>6.4908126</v>
       </c>
       <c r="N19">
-        <v>78.06978809999998</v>
+        <v>77.70918739999999</v>
       </c>
       <c r="O19">
-        <v>14.833259739</v>
+        <v>14.764745606</v>
       </c>
       <c r="P19">
-        <v>63.23652836099998</v>
+        <v>62.94444179399999</v>
       </c>
       <c r="Q19">
-        <v>132.036528361</v>
+        <v>131.744441794</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09699430006751733</v>
+        <v>0.09751687916573977</v>
       </c>
       <c r="T19">
-        <v>0.9376415844321523</v>
+        <v>0.9472128041382952</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.73525114197113</v>
+        <v>12.97218163408384</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08729758091590663</v>
+        <v>0.08739443277577386</v>
       </c>
       <c r="C20">
-        <v>597.8178379444507</v>
+        <v>589.1784955054502</v>
       </c>
       <c r="D20">
-        <v>631.4598379444508</v>
+        <v>629.9894955054502</v>
       </c>
       <c r="E20">
-        <v>-359.958</v>
+        <v>-352.789</v>
       </c>
       <c r="F20">
-        <v>129.042</v>
+        <v>136.211</v>
       </c>
       <c r="G20">
         <v>95.40000000000001</v>
@@ -2927,45 +2927,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M20">
-        <v>6.4908126</v>
+        <v>7.055729799999999</v>
       </c>
       <c r="N20">
-        <v>77.70918739999999</v>
+        <v>77.14427019999999</v>
       </c>
       <c r="O20">
-        <v>14.764745606</v>
+        <v>14.657411338</v>
       </c>
       <c r="P20">
-        <v>62.94444179399999</v>
+        <v>62.48685886199999</v>
       </c>
       <c r="Q20">
-        <v>131.744441794</v>
+        <v>131.286858862</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09751687916573977</v>
+        <v>0.09805236145157266</v>
       </c>
       <c r="T20">
-        <v>0.9472128041382952</v>
+        <v>0.9570203502569358</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.97218163408384</v>
+        <v>11.93356355567924</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08739443277577386</v>
+        <v>0.0872725846356411</v>
       </c>
       <c r="C21">
-        <v>589.1784955054502</v>
+        <v>583.8604302616251</v>
       </c>
       <c r="D21">
-        <v>629.9894955054502</v>
+        <v>631.8404302616251</v>
       </c>
       <c r="E21">
-        <v>-352.789</v>
+        <v>-345.62</v>
       </c>
       <c r="F21">
-        <v>136.211</v>
+        <v>143.38</v>
       </c>
       <c r="G21">
         <v>95.40000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M21">
-        <v>7.055729799999999</v>
+        <v>7.427084</v>
       </c>
       <c r="N21">
-        <v>77.14427019999999</v>
+        <v>76.772916</v>
       </c>
       <c r="O21">
-        <v>14.657411338</v>
+        <v>14.58685404</v>
       </c>
       <c r="P21">
-        <v>62.48685886199999</v>
+        <v>62.18606196</v>
       </c>
       <c r="Q21">
-        <v>131.286858862</v>
+        <v>130.98606196</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09805236145157266</v>
+        <v>0.09860123079455137</v>
       </c>
       <c r="T21">
-        <v>0.9570203502569358</v>
+        <v>0.9670730850285424</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.93356355567924</v>
+        <v>11.33688537789528</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0872725846356411</v>
+        <v>0.08715073649550834</v>
       </c>
       <c r="C22">
-        <v>583.8604302616251</v>
+        <v>578.553273309969</v>
       </c>
       <c r="D22">
-        <v>631.8404302616251</v>
+        <v>633.702273309969</v>
       </c>
       <c r="E22">
-        <v>-345.62</v>
+        <v>-338.451</v>
       </c>
       <c r="F22">
-        <v>143.38</v>
+        <v>150.549</v>
       </c>
       <c r="G22">
         <v>95.40000000000001</v>
@@ -3091,28 +3091,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M22">
-        <v>7.427084</v>
+        <v>7.798438200000001</v>
       </c>
       <c r="N22">
-        <v>76.772916</v>
+        <v>76.40156179999998</v>
       </c>
       <c r="O22">
-        <v>14.58685404</v>
+        <v>14.516296742</v>
       </c>
       <c r="P22">
-        <v>62.18606196</v>
+        <v>61.88526505799999</v>
       </c>
       <c r="Q22">
-        <v>130.98606196</v>
+        <v>130.685265058</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09860123079455137</v>
+        <v>0.0991639955639346</v>
       </c>
       <c r="T22">
-        <v>0.9670730850285424</v>
+        <v>0.9773803194146198</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.33688537789528</v>
+        <v>10.7970336932336</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08715073649550834</v>
+        <v>0.08702888835537557</v>
       </c>
       <c r="C23">
-        <v>578.553273309969</v>
+        <v>573.2571213658069</v>
       </c>
       <c r="D23">
-        <v>633.702273309969</v>
+        <v>635.5751213658069</v>
       </c>
       <c r="E23">
-        <v>-338.451</v>
+        <v>-331.282</v>
       </c>
       <c r="F23">
-        <v>150.549</v>
+        <v>157.718</v>
       </c>
       <c r="G23">
         <v>95.40000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M23">
-        <v>7.798438199999999</v>
+        <v>8.169792399999999</v>
       </c>
       <c r="N23">
-        <v>76.4015618</v>
+        <v>76.03020759999998</v>
       </c>
       <c r="O23">
-        <v>14.516296742</v>
+        <v>14.445739444</v>
       </c>
       <c r="P23">
-        <v>61.88526505799999</v>
+        <v>61.58446815599999</v>
       </c>
       <c r="Q23">
-        <v>130.685265058</v>
+        <v>130.384468156</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0991639955639346</v>
+        <v>0.09974119019919944</v>
       </c>
       <c r="T23">
-        <v>0.9773803194146198</v>
+        <v>0.9879518418618788</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.7970336932336</v>
+        <v>10.30625943445026</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08702888835537557</v>
+        <v>0.08690704021524279</v>
       </c>
       <c r="C24">
-        <v>573.2571213658069</v>
+        <v>567.9720722911857</v>
       </c>
       <c r="D24">
-        <v>635.5751213658069</v>
+        <v>637.4590722911857</v>
       </c>
       <c r="E24">
-        <v>-331.282</v>
+        <v>-324.113</v>
       </c>
       <c r="F24">
-        <v>157.718</v>
+        <v>164.887</v>
       </c>
       <c r="G24">
         <v>95.40000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M24">
-        <v>8.169792399999999</v>
+        <v>8.541146599999999</v>
       </c>
       <c r="N24">
-        <v>76.03020759999998</v>
+        <v>75.65885339999998</v>
       </c>
       <c r="O24">
-        <v>14.445739444</v>
+        <v>14.375182146</v>
       </c>
       <c r="P24">
-        <v>61.58446815599999</v>
+        <v>61.28367125399998</v>
       </c>
       <c r="Q24">
-        <v>130.384468156</v>
+        <v>130.083671254</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09974119019919944</v>
+        <v>0.1003333769029127</v>
       </c>
       <c r="T24">
-        <v>0.9879518418618788</v>
+        <v>0.9987979493077678</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.30625943445026</v>
+        <v>9.858161198169809</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08690704021524279</v>
+        <v>0.08711567207511005</v>
       </c>
       <c r="C25">
-        <v>567.9720722911857</v>
+        <v>557.5840935075514</v>
       </c>
       <c r="D25">
-        <v>637.4590722911857</v>
+        <v>634.2400935075515</v>
       </c>
       <c r="E25">
-        <v>-324.113</v>
+        <v>-316.944</v>
       </c>
       <c r="F25">
-        <v>164.887</v>
+        <v>172.056</v>
       </c>
       <c r="G25">
         <v>95.40000000000001</v>
@@ -3337,45 +3337,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M25">
-        <v>8.541146599999999</v>
+        <v>9.204996000000001</v>
       </c>
       <c r="N25">
-        <v>75.65885339999998</v>
+        <v>74.99500399999999</v>
       </c>
       <c r="O25">
-        <v>14.375182146</v>
+        <v>14.24905076</v>
       </c>
       <c r="P25">
-        <v>61.28367125399998</v>
+        <v>60.74595323999999</v>
       </c>
       <c r="Q25">
-        <v>130.083671254</v>
+        <v>129.54595324</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1003333769029127</v>
+        <v>0.1009411474672501</v>
       </c>
       <c r="T25">
-        <v>0.9987979493077678</v>
+        <v>1.009929480633812</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.858161198169809</v>
+        <v>9.147206582164728</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08711567207511005</v>
+        <v>0.08700759393497727</v>
       </c>
       <c r="C26">
-        <v>557.5840935075514</v>
+        <v>552.0785609211573</v>
       </c>
       <c r="D26">
-        <v>634.2400935075515</v>
+        <v>635.9035609211574</v>
       </c>
       <c r="E26">
-        <v>-316.944</v>
+        <v>-309.775</v>
       </c>
       <c r="F26">
-        <v>172.056</v>
+        <v>179.225</v>
       </c>
       <c r="G26">
         <v>95.40000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M26">
-        <v>9.204996</v>
+        <v>9.588537499999999</v>
       </c>
       <c r="N26">
-        <v>74.99500399999999</v>
+        <v>74.61146249999999</v>
       </c>
       <c r="O26">
-        <v>14.24905076</v>
+        <v>14.176177875</v>
       </c>
       <c r="P26">
-        <v>60.74595323999999</v>
+        <v>60.43528462499999</v>
       </c>
       <c r="Q26">
-        <v>129.54595324</v>
+        <v>129.235284625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1009411474672501</v>
+        <v>0.1015651252466364</v>
       </c>
       <c r="T26">
-        <v>1.009929480633812</v>
+        <v>1.021357852795217</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.147206582164729</v>
+        <v>8.781318318878139</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08700759393497727</v>
+        <v>0.08689951579484452</v>
       </c>
       <c r="C27">
-        <v>552.0785609211573</v>
+        <v>546.581777073562</v>
       </c>
       <c r="D27">
-        <v>635.9035609211574</v>
+        <v>637.575777073562</v>
       </c>
       <c r="E27">
-        <v>-309.775</v>
+        <v>-302.606</v>
       </c>
       <c r="F27">
-        <v>179.225</v>
+        <v>186.394</v>
       </c>
       <c r="G27">
         <v>95.40000000000001</v>
@@ -3501,28 +3501,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M27">
-        <v>9.588537499999999</v>
+        <v>9.972079000000001</v>
       </c>
       <c r="N27">
-        <v>74.61146249999999</v>
+        <v>74.22792099999998</v>
       </c>
       <c r="O27">
-        <v>14.176177875</v>
+        <v>14.10330499</v>
       </c>
       <c r="P27">
-        <v>60.43528462499999</v>
+        <v>60.12461600999998</v>
       </c>
       <c r="Q27">
-        <v>129.235284625</v>
+        <v>128.92461601</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1015651252466364</v>
+        <v>0.1022059672903304</v>
       </c>
       <c r="T27">
-        <v>1.021357852795217</v>
+        <v>1.033095099879904</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.781318318878139</v>
+        <v>8.443575306613592</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08689951579484452</v>
+        <v>0.08679143765471174</v>
       </c>
       <c r="C28">
-        <v>546.581777073562</v>
+        <v>541.0938111656147</v>
       </c>
       <c r="D28">
-        <v>637.575777073562</v>
+        <v>639.2568111656147</v>
       </c>
       <c r="E28">
-        <v>-302.606</v>
+        <v>-295.437</v>
       </c>
       <c r="F28">
-        <v>186.394</v>
+        <v>193.563</v>
       </c>
       <c r="G28">
         <v>95.40000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M28">
-        <v>9.972079000000001</v>
+        <v>10.3556205</v>
       </c>
       <c r="N28">
-        <v>74.22792099999998</v>
+        <v>73.84437949999999</v>
       </c>
       <c r="O28">
-        <v>14.10330499</v>
+        <v>14.030432105</v>
       </c>
       <c r="P28">
-        <v>60.12461600999998</v>
+        <v>59.81394739499999</v>
       </c>
       <c r="Q28">
-        <v>128.92461601</v>
+        <v>128.613947395</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1022059672903304</v>
+        <v>0.1028643666502901</v>
       </c>
       <c r="T28">
-        <v>1.033095099879904</v>
+        <v>1.045153915377869</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.443575306613592</v>
+        <v>8.130850295257535</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08679143765471174</v>
+        <v>0.08668335951457898</v>
       </c>
       <c r="C29">
-        <v>541.0938111656147</v>
+        <v>535.6147331299128</v>
       </c>
       <c r="D29">
-        <v>639.2568111656147</v>
+        <v>640.9467331299128</v>
       </c>
       <c r="E29">
-        <v>-295.437</v>
+        <v>-288.268</v>
       </c>
       <c r="F29">
-        <v>193.563</v>
+        <v>200.732</v>
       </c>
       <c r="G29">
         <v>95.40000000000001</v>
@@ -3665,28 +3665,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M29">
-        <v>10.3556205</v>
+        <v>10.739162</v>
       </c>
       <c r="N29">
-        <v>73.84437949999999</v>
+        <v>73.460838</v>
       </c>
       <c r="O29">
-        <v>14.030432105</v>
+        <v>13.95755922</v>
       </c>
       <c r="P29">
-        <v>59.81394739499999</v>
+        <v>59.50327878</v>
       </c>
       <c r="Q29">
-        <v>128.613947395</v>
+        <v>128.30327878</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1028643666502901</v>
+        <v>0.1035410548813597</v>
       </c>
       <c r="T29">
-        <v>1.045153915377869</v>
+        <v>1.057547697973001</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.130850295257535</v>
+        <v>7.840462784712624</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08668335951457898</v>
+        <v>0.08676320137444624</v>
       </c>
       <c r="C30">
-        <v>535.6147331299128</v>
+        <v>527.196456278205</v>
       </c>
       <c r="D30">
-        <v>640.9467331299128</v>
+        <v>639.6974562782051</v>
       </c>
       <c r="E30">
-        <v>-288.268</v>
+        <v>-281.099</v>
       </c>
       <c r="F30">
-        <v>200.732</v>
+        <v>207.901</v>
       </c>
       <c r="G30">
         <v>95.40000000000001</v>
@@ -3747,45 +3747,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M30">
-        <v>10.739162</v>
+        <v>11.2890243</v>
       </c>
       <c r="N30">
-        <v>73.460838</v>
+        <v>72.91097569999999</v>
       </c>
       <c r="O30">
-        <v>13.95755922</v>
+        <v>13.853085383</v>
       </c>
       <c r="P30">
-        <v>59.50327878</v>
+        <v>59.05789031699999</v>
       </c>
       <c r="Q30">
-        <v>128.30327878</v>
+        <v>127.857890317</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1035410548813597</v>
+        <v>0.1042368047527412</v>
       </c>
       <c r="T30">
-        <v>1.057547697973001</v>
+        <v>1.070290601204615</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.840462784712624</v>
+        <v>7.45857195116499</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08676320137444624</v>
+        <v>0.08666160323431345</v>
       </c>
       <c r="C31">
-        <v>527.1964562782051</v>
+        <v>521.6179976828794</v>
       </c>
       <c r="D31">
-        <v>639.6974562782051</v>
+        <v>641.2879976828793</v>
       </c>
       <c r="E31">
-        <v>-281.099</v>
+        <v>-273.93</v>
       </c>
       <c r="F31">
-        <v>207.901</v>
+        <v>215.07</v>
       </c>
       <c r="G31">
         <v>95.40000000000001</v>
@@ -3829,28 +3829,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M31">
-        <v>11.2890243</v>
+        <v>11.678301</v>
       </c>
       <c r="N31">
-        <v>72.91097569999999</v>
+        <v>72.52169899999998</v>
       </c>
       <c r="O31">
-        <v>13.853085383</v>
+        <v>13.77912281</v>
       </c>
       <c r="P31">
-        <v>59.05789031699999</v>
+        <v>58.74257618999999</v>
       </c>
       <c r="Q31">
-        <v>127.857890317</v>
+        <v>127.54257619</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1042368047527412</v>
+        <v>0.1049524331918764</v>
       </c>
       <c r="T31">
-        <v>1.070290601204614</v>
+        <v>1.083397587385703</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.458571951164991</v>
+        <v>7.209952886126157</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08666160323431345</v>
+        <v>0.0865600050941807</v>
       </c>
       <c r="C32">
-        <v>521.6179976828794</v>
+        <v>516.0474682351642</v>
       </c>
       <c r="D32">
-        <v>641.2879976828793</v>
+        <v>642.8864682351642</v>
       </c>
       <c r="E32">
-        <v>-273.93</v>
+        <v>-266.761</v>
       </c>
       <c r="F32">
-        <v>215.07</v>
+        <v>222.239</v>
       </c>
       <c r="G32">
         <v>95.40000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M32">
-        <v>11.678301</v>
+        <v>12.0675777</v>
       </c>
       <c r="N32">
-        <v>72.52169899999998</v>
+        <v>72.13242229999999</v>
       </c>
       <c r="O32">
-        <v>13.77912281</v>
+        <v>13.705160237</v>
       </c>
       <c r="P32">
-        <v>58.74257618999999</v>
+        <v>58.42726206299999</v>
       </c>
       <c r="Q32">
-        <v>127.54257619</v>
+        <v>127.227262063</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1049524331918764</v>
+        <v>0.1056888044843199</v>
       </c>
       <c r="T32">
-        <v>1.083397587385703</v>
+        <v>1.096884486209722</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.209952886126157</v>
+        <v>6.977373760767248</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0865600050941807</v>
+        <v>0.08645840695404793</v>
       </c>
       <c r="C33">
-        <v>516.0474682351642</v>
+        <v>510.4849273756573</v>
       </c>
       <c r="D33">
-        <v>642.8864682351642</v>
+        <v>644.4929273756574</v>
       </c>
       <c r="E33">
-        <v>-266.761</v>
+        <v>-259.592</v>
       </c>
       <c r="F33">
-        <v>222.239</v>
+        <v>229.408</v>
       </c>
       <c r="G33">
         <v>95.40000000000001</v>
@@ -3993,28 +3993,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M33">
-        <v>12.0675777</v>
+        <v>12.4568544</v>
       </c>
       <c r="N33">
-        <v>72.13242229999999</v>
+        <v>71.74314559999999</v>
       </c>
       <c r="O33">
-        <v>13.705160237</v>
+        <v>13.631197664</v>
       </c>
       <c r="P33">
-        <v>58.42726206299999</v>
+        <v>58.11194793599999</v>
       </c>
       <c r="Q33">
-        <v>127.227262063</v>
+        <v>126.911947936</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1056888044843199</v>
+        <v>0.1064468337559528</v>
       </c>
       <c r="T33">
-        <v>1.096884486209722</v>
+        <v>1.110768058528564</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.977373760767248</v>
+        <v>6.759330830743273</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08645840695404793</v>
+        <v>0.08635680881391518</v>
       </c>
       <c r="C34">
-        <v>510.4849273756573</v>
+        <v>504.9304351405684</v>
       </c>
       <c r="D34">
-        <v>644.4929273756574</v>
+        <v>646.1074351405684</v>
       </c>
       <c r="E34">
-        <v>-259.592</v>
+        <v>-252.423</v>
       </c>
       <c r="F34">
-        <v>229.408</v>
+        <v>236.577</v>
       </c>
       <c r="G34">
         <v>95.40000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M34">
-        <v>12.4568544</v>
+        <v>12.8461311</v>
       </c>
       <c r="N34">
-        <v>71.74314559999999</v>
+        <v>71.35386889999998</v>
       </c>
       <c r="O34">
-        <v>13.631197664</v>
+        <v>13.557235091</v>
       </c>
       <c r="P34">
-        <v>58.11194793599999</v>
+        <v>57.79663380899999</v>
       </c>
       <c r="Q34">
-        <v>126.911947936</v>
+        <v>126.596633809</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064468337559528</v>
+        <v>0.1072274907670376</v>
       </c>
       <c r="T34">
-        <v>1.110768058528564</v>
+        <v>1.125066065841999</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.759330830743273</v>
+        <v>6.554502623751051</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08635680881391518</v>
+        <v>0.08625521067378242</v>
       </c>
       <c r="C35">
-        <v>504.9304351405684</v>
+        <v>499.3840521692018</v>
       </c>
       <c r="D35">
-        <v>646.1074351405684</v>
+        <v>647.7300521692018</v>
       </c>
       <c r="E35">
-        <v>-252.423</v>
+        <v>-245.254</v>
       </c>
       <c r="F35">
-        <v>236.577</v>
+        <v>243.746</v>
       </c>
       <c r="G35">
         <v>95.40000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M35">
-        <v>12.8461311</v>
+        <v>13.2354078</v>
       </c>
       <c r="N35">
-        <v>71.35386889999998</v>
+        <v>70.96459219999998</v>
       </c>
       <c r="O35">
-        <v>13.557235091</v>
+        <v>13.483272518</v>
       </c>
       <c r="P35">
-        <v>57.79663380899999</v>
+        <v>57.48131968199998</v>
       </c>
       <c r="Q35">
-        <v>126.596633809</v>
+        <v>126.281319682</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1072274907670376</v>
+        <v>0.1080318040511855</v>
       </c>
       <c r="T35">
-        <v>1.125066065841999</v>
+        <v>1.139797346104326</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.554502623751051</v>
+        <v>6.361723134817197</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08625521067378242</v>
+        <v>0.08615361253364964</v>
       </c>
       <c r="C36">
-        <v>499.3840521692018</v>
+        <v>493.8458397115468</v>
       </c>
       <c r="D36">
-        <v>647.7300521692018</v>
+        <v>649.3608397115469</v>
       </c>
       <c r="E36">
-        <v>-245.254</v>
+        <v>-238.085</v>
       </c>
       <c r="F36">
-        <v>243.746</v>
+        <v>250.915</v>
       </c>
       <c r="G36">
         <v>95.40000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M36">
-        <v>13.2354078</v>
+        <v>13.6246845</v>
       </c>
       <c r="N36">
-        <v>70.96459219999998</v>
+        <v>70.57531549999999</v>
       </c>
       <c r="O36">
-        <v>13.483272518</v>
+        <v>13.409309945</v>
       </c>
       <c r="P36">
-        <v>57.48131968199998</v>
+        <v>57.16600555499999</v>
       </c>
       <c r="Q36">
-        <v>126.281319682</v>
+        <v>125.966005555</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1080318040511855</v>
+        <v>0.1088608654363841</v>
       </c>
       <c r="T36">
-        <v>1.139797346104326</v>
+        <v>1.154981896528571</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.361723134817197</v>
+        <v>6.179959616679563</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08615361253364964</v>
+        <v>0.0863436143935169</v>
       </c>
       <c r="C37">
-        <v>493.8458397115468</v>
+        <v>483.6337028547134</v>
       </c>
       <c r="D37">
-        <v>649.3608397115469</v>
+        <v>646.3177028547134</v>
       </c>
       <c r="E37">
-        <v>-238.085</v>
+        <v>-230.916</v>
       </c>
       <c r="F37">
-        <v>250.915</v>
+        <v>258.084</v>
       </c>
       <c r="G37">
         <v>95.40000000000001</v>
@@ -4321,45 +4321,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M37">
-        <v>13.6246845</v>
+        <v>14.2720452</v>
       </c>
       <c r="N37">
-        <v>70.57531549999999</v>
+        <v>69.92795479999998</v>
       </c>
       <c r="O37">
-        <v>13.409309945</v>
+        <v>13.286311412</v>
       </c>
       <c r="P37">
-        <v>57.16600555499999</v>
+        <v>56.64164338799998</v>
       </c>
       <c r="Q37">
-        <v>125.966005555</v>
+        <v>125.441643388</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1088608654363841</v>
+        <v>0.1097158349898701</v>
       </c>
       <c r="T37">
-        <v>1.154981896528571</v>
+        <v>1.170640964153573</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.179959616679563</v>
+        <v>5.899644992716249</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08634361439351687</v>
+        <v>0.08625011625338413</v>
       </c>
       <c r="C38">
-        <v>483.6337028547138</v>
+        <v>477.9586294178228</v>
       </c>
       <c r="D38">
-        <v>646.3177028547138</v>
+        <v>647.8116294178228</v>
       </c>
       <c r="E38">
-        <v>-230.916</v>
+        <v>-223.747</v>
       </c>
       <c r="F38">
-        <v>258.084</v>
+        <v>265.253</v>
       </c>
       <c r="G38">
         <v>95.40000000000001</v>
@@ -4403,28 +4403,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M38">
-        <v>14.2720452</v>
+        <v>14.6684909</v>
       </c>
       <c r="N38">
-        <v>69.92795479999998</v>
+        <v>69.53150909999999</v>
       </c>
       <c r="O38">
-        <v>13.286311412</v>
+        <v>13.210986729</v>
       </c>
       <c r="P38">
-        <v>56.64164338799998</v>
+        <v>56.320522371</v>
       </c>
       <c r="Q38">
-        <v>125.441643388</v>
+        <v>125.120522371</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1097158349898701</v>
+        <v>0.1105979464339431</v>
       </c>
       <c r="T38">
-        <v>1.170640964153573</v>
+        <v>1.186797145036512</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.899644992716249</v>
+        <v>5.740195128048243</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08625011625338413</v>
+        <v>0.08615661811325137</v>
       </c>
       <c r="C39">
-        <v>477.9586294178228</v>
+        <v>472.2904782336718</v>
       </c>
       <c r="D39">
-        <v>647.8116294178228</v>
+        <v>649.3124782336718</v>
       </c>
       <c r="E39">
-        <v>-223.747</v>
+        <v>-216.578</v>
       </c>
       <c r="F39">
-        <v>265.253</v>
+        <v>272.422</v>
       </c>
       <c r="G39">
         <v>95.40000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M39">
-        <v>14.6684909</v>
+        <v>15.0649366</v>
       </c>
       <c r="N39">
-        <v>69.53150909999999</v>
+        <v>69.13506339999999</v>
       </c>
       <c r="O39">
-        <v>13.210986729</v>
+        <v>13.135662046</v>
       </c>
       <c r="P39">
-        <v>56.320522371</v>
+        <v>55.99940135399999</v>
       </c>
       <c r="Q39">
-        <v>125.120522371</v>
+        <v>124.799401354</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1105979464339431</v>
+        <v>0.1115085130858893</v>
       </c>
       <c r="T39">
-        <v>1.186797145036512</v>
+        <v>1.203474493044707</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.740195128048243</v>
+        <v>5.589137361520658</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08615661811325137</v>
+        <v>0.08606311997311861</v>
       </c>
       <c r="C40">
-        <v>472.2904782336718</v>
+        <v>466.6292975263738</v>
       </c>
       <c r="D40">
-        <v>649.3124782336718</v>
+        <v>650.8202975263738</v>
       </c>
       <c r="E40">
-        <v>-216.578</v>
+        <v>-209.409</v>
       </c>
       <c r="F40">
-        <v>272.422</v>
+        <v>279.591</v>
       </c>
       <c r="G40">
         <v>95.40000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M40">
-        <v>15.0649366</v>
+        <v>15.4613823</v>
       </c>
       <c r="N40">
-        <v>69.13506339999999</v>
+        <v>68.73861769999999</v>
       </c>
       <c r="O40">
-        <v>13.135662046</v>
+        <v>13.060337363</v>
       </c>
       <c r="P40">
-        <v>55.99940135399999</v>
+        <v>55.67828033699999</v>
       </c>
       <c r="Q40">
-        <v>124.799401354</v>
+        <v>124.478280337</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1115085130858893</v>
+        <v>0.1124489343821616</v>
       </c>
       <c r="T40">
-        <v>1.203474493044707</v>
+        <v>1.220698639348253</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.589137361520658</v>
+        <v>5.445826147122692</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08606311997311861</v>
+        <v>0.08596962183298584</v>
       </c>
       <c r="C41">
-        <v>466.6292975263738</v>
+        <v>460.975135969025</v>
       </c>
       <c r="D41">
-        <v>650.8202975263738</v>
+        <v>652.335135969025</v>
       </c>
       <c r="E41">
-        <v>-209.409</v>
+        <v>-202.24</v>
       </c>
       <c r="F41">
-        <v>279.591</v>
+        <v>286.76</v>
       </c>
       <c r="G41">
         <v>95.40000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M41">
-        <v>15.4613823</v>
+        <v>15.857828</v>
       </c>
       <c r="N41">
-        <v>68.73861769999999</v>
+        <v>68.34217199999999</v>
       </c>
       <c r="O41">
-        <v>13.060337363</v>
+        <v>12.98501268</v>
       </c>
       <c r="P41">
-        <v>55.67828033699999</v>
+        <v>55.35715931999999</v>
       </c>
       <c r="Q41">
-        <v>124.478280337</v>
+        <v>124.15715932</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1124489343821616</v>
+        <v>0.1134207030549764</v>
       </c>
       <c r="T41">
-        <v>1.220698639348253</v>
+        <v>1.238496923861917</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.445826147122692</v>
+        <v>5.309680493444625</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08596962183298584</v>
+        <v>0.08587612369285308</v>
       </c>
       <c r="C42">
-        <v>460.975135969025</v>
+        <v>455.3280426889414</v>
       </c>
       <c r="D42">
-        <v>652.335135969025</v>
+        <v>653.8570426889414</v>
       </c>
       <c r="E42">
-        <v>-202.24</v>
+        <v>-195.071</v>
       </c>
       <c r="F42">
-        <v>286.76</v>
+        <v>293.929</v>
       </c>
       <c r="G42">
         <v>95.40000000000001</v>
@@ -4731,28 +4731,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M42">
-        <v>15.857828</v>
+        <v>16.2542737</v>
       </c>
       <c r="N42">
-        <v>68.34217199999999</v>
+        <v>67.94572629999999</v>
       </c>
       <c r="O42">
-        <v>12.98501268</v>
+        <v>12.909687997</v>
       </c>
       <c r="P42">
-        <v>55.35715931999999</v>
+        <v>55.03603830299999</v>
       </c>
       <c r="Q42">
-        <v>124.15715932</v>
+        <v>123.836038303</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1134207030549764</v>
+        <v>0.114425413038734</v>
       </c>
       <c r="T42">
-        <v>1.238496923861917</v>
+        <v>1.25689854005401</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.309680493444625</v>
+        <v>5.180176091165487</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08587612369285308</v>
+        <v>0.08578262555272032</v>
       </c>
       <c r="C43">
-        <v>455.3280426889414</v>
+        <v>449.6880672729702</v>
       </c>
       <c r="D43">
-        <v>653.8570426889414</v>
+        <v>655.3860672729702</v>
       </c>
       <c r="E43">
-        <v>-195.071</v>
+        <v>-187.902</v>
       </c>
       <c r="F43">
-        <v>293.929</v>
+        <v>301.098</v>
       </c>
       <c r="G43">
         <v>95.40000000000001</v>
@@ -4813,28 +4813,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M43">
-        <v>16.2542737</v>
+        <v>16.6507194</v>
       </c>
       <c r="N43">
-        <v>67.94572629999999</v>
+        <v>67.54928059999999</v>
       </c>
       <c r="O43">
-        <v>12.909687997</v>
+        <v>12.834363314</v>
       </c>
       <c r="P43">
-        <v>55.03603830299999</v>
+        <v>54.71491728599999</v>
       </c>
       <c r="Q43">
-        <v>123.836038303</v>
+        <v>123.514917286</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.114425413038734</v>
+        <v>0.1154647681943454</v>
       </c>
       <c r="T43">
-        <v>1.25689854005401</v>
+        <v>1.275934694735486</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.180176091165487</v>
+        <v>5.056838565185357</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08578262555272032</v>
+        <v>0.08568912741258755</v>
       </c>
       <c r="C44">
-        <v>449.6880672729702</v>
+        <v>444.0552597728746</v>
       </c>
       <c r="D44">
-        <v>655.3860672729702</v>
+        <v>656.9222597728747</v>
       </c>
       <c r="E44">
-        <v>-187.902</v>
+        <v>-180.733</v>
       </c>
       <c r="F44">
-        <v>301.098</v>
+        <v>308.267</v>
       </c>
       <c r="G44">
         <v>95.40000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M44">
-        <v>16.6507194</v>
+        <v>17.0471651</v>
       </c>
       <c r="N44">
-        <v>67.54928059999999</v>
+        <v>67.15283489999999</v>
       </c>
       <c r="O44">
-        <v>12.834363314</v>
+        <v>12.759038631</v>
       </c>
       <c r="P44">
-        <v>54.71491728599999</v>
+        <v>54.39379626899999</v>
       </c>
       <c r="Q44">
-        <v>123.514917286</v>
+        <v>123.193796269</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1154647681943453</v>
+        <v>0.116540591951908</v>
       </c>
       <c r="T44">
-        <v>1.275934694735486</v>
+        <v>1.295638784668943</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.056838565185357</v>
+        <v>4.939237668320581</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08568912741258755</v>
+        <v>0.08559562927245477</v>
       </c>
       <c r="C45">
-        <v>444.0552597728746</v>
+        <v>438.4296707107964</v>
       </c>
       <c r="D45">
-        <v>656.9222597728747</v>
+        <v>658.4656707107964</v>
       </c>
       <c r="E45">
-        <v>-180.733</v>
+        <v>-173.564</v>
       </c>
       <c r="F45">
-        <v>308.267</v>
+        <v>315.436</v>
       </c>
       <c r="G45">
         <v>95.40000000000001</v>
@@ -4977,28 +4977,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M45">
-        <v>17.0471651</v>
+        <v>17.4436108</v>
       </c>
       <c r="N45">
-        <v>67.15283489999999</v>
+        <v>66.75638919999999</v>
       </c>
       <c r="O45">
-        <v>12.759038631</v>
+        <v>12.683713948</v>
       </c>
       <c r="P45">
-        <v>54.39379626899999</v>
+        <v>54.07267525199999</v>
       </c>
       <c r="Q45">
-        <v>123.193796269</v>
+        <v>122.872675252</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.116540591951908</v>
+        <v>0.1176548379865264</v>
       </c>
       <c r="T45">
-        <v>1.295638784668943</v>
+        <v>1.316046592100024</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.939237668320581</v>
+        <v>4.826982266767841</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08559562927245477</v>
+        <v>0.08550213113232201</v>
       </c>
       <c r="C46">
-        <v>438.4296707107964</v>
+        <v>432.8113510847929</v>
       </c>
       <c r="D46">
-        <v>658.4656707107964</v>
+        <v>660.016351084793</v>
       </c>
       <c r="E46">
-        <v>-173.564</v>
+        <v>-166.395</v>
       </c>
       <c r="F46">
-        <v>315.436</v>
+        <v>322.605</v>
       </c>
       <c r="G46">
         <v>95.40000000000001</v>
@@ -5059,28 +5059,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M46">
-        <v>17.4436108</v>
+        <v>17.8400565</v>
       </c>
       <c r="N46">
-        <v>66.75638919999999</v>
+        <v>66.35994349999999</v>
       </c>
       <c r="O46">
-        <v>12.683713948</v>
+        <v>12.608389265</v>
       </c>
       <c r="P46">
-        <v>54.07267525199999</v>
+        <v>53.75155423499999</v>
       </c>
       <c r="Q46">
-        <v>122.872675252</v>
+        <v>122.551554235</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1176548379865264</v>
+        <v>0.1188096020587673</v>
       </c>
       <c r="T46">
-        <v>1.316046592100024</v>
+        <v>1.337196501619508</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.826982266767841</v>
+        <v>4.719715994172999</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08550213113232201</v>
+        <v>0.08540863299218926</v>
       </c>
       <c r="C47">
-        <v>432.8113510847929</v>
+        <v>427.2003523744563</v>
       </c>
       <c r="D47">
-        <v>660.016351084793</v>
+        <v>661.5743523744563</v>
       </c>
       <c r="E47">
-        <v>-166.395</v>
+        <v>-159.226</v>
       </c>
       <c r="F47">
-        <v>322.605</v>
+        <v>329.774</v>
       </c>
       <c r="G47">
         <v>95.40000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M47">
-        <v>17.8400565</v>
+        <v>18.2365022</v>
       </c>
       <c r="N47">
-        <v>66.35994349999999</v>
+        <v>65.96349779999998</v>
       </c>
       <c r="O47">
-        <v>12.608389265</v>
+        <v>12.533064582</v>
       </c>
       <c r="P47">
-        <v>53.75155423499999</v>
+        <v>53.43043321799999</v>
       </c>
       <c r="Q47">
-        <v>122.551554235</v>
+        <v>122.230433218</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1188096020587673</v>
+        <v>0.1200071351707208</v>
       </c>
       <c r="T47">
-        <v>1.337196501619508</v>
+        <v>1.359129741121194</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.719715994172999</v>
+        <v>4.617113472560543</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08540863299218926</v>
+        <v>0.0853151348520565</v>
       </c>
       <c r="C48">
-        <v>427.2003523744563</v>
+        <v>421.5967265466093</v>
       </c>
       <c r="D48">
-        <v>661.5743523744563</v>
+        <v>663.1397265466093</v>
       </c>
       <c r="E48">
-        <v>-159.226</v>
+        <v>-152.057</v>
       </c>
       <c r="F48">
-        <v>329.774</v>
+        <v>336.943</v>
       </c>
       <c r="G48">
         <v>95.40000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M48">
-        <v>18.2365022</v>
+        <v>18.6329479</v>
       </c>
       <c r="N48">
-        <v>65.96349779999998</v>
+        <v>65.56705209999998</v>
       </c>
       <c r="O48">
-        <v>12.533064582</v>
+        <v>12.457739899</v>
       </c>
       <c r="P48">
-        <v>53.43043321799999</v>
+        <v>53.10931220099999</v>
       </c>
       <c r="Q48">
-        <v>122.230433218</v>
+        <v>121.909312201</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1200071351707208</v>
+        <v>0.1212498582114273</v>
       </c>
       <c r="T48">
-        <v>1.359129741121194</v>
+        <v>1.381890650038039</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.617113472560543</v>
+        <v>4.518877015697552</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0853151348520565</v>
+        <v>0.08619363671192373</v>
       </c>
       <c r="C49">
-        <v>421.5967265466093</v>
+        <v>400.0054182192414</v>
       </c>
       <c r="D49">
-        <v>663.1397265466093</v>
+        <v>648.7174182192415</v>
       </c>
       <c r="E49">
-        <v>-152.057</v>
+        <v>-144.888</v>
       </c>
       <c r="F49">
-        <v>336.943</v>
+        <v>344.112</v>
       </c>
       <c r="G49">
         <v>95.40000000000001</v>
@@ -5305,45 +5305,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M49">
-        <v>18.6329479</v>
+        <v>19.8896736</v>
       </c>
       <c r="N49">
-        <v>65.56705209999998</v>
+        <v>64.31032639999998</v>
       </c>
       <c r="O49">
-        <v>12.457739899</v>
+        <v>12.218962016</v>
       </c>
       <c r="P49">
-        <v>53.10931220099999</v>
+        <v>52.09136438399999</v>
       </c>
       <c r="Q49">
-        <v>121.909312201</v>
+        <v>120.891364384</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1212498582114273</v>
+        <v>0.122540378292161</v>
       </c>
       <c r="T49">
-        <v>1.381890650038039</v>
+        <v>1.405526978528609</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.19</v>
       </c>
       <c r="W49">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.518877015697552</v>
+        <v>4.233352527212913</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08619363671192372</v>
+        <v>0.08612038857179097</v>
       </c>
       <c r="C50">
-        <v>400.0054182192417</v>
+        <v>394.0149124262524</v>
       </c>
       <c r="D50">
-        <v>648.7174182192417</v>
+        <v>649.8959124262524</v>
       </c>
       <c r="E50">
-        <v>-144.888</v>
+        <v>-137.719</v>
       </c>
       <c r="F50">
-        <v>344.112</v>
+        <v>351.281</v>
       </c>
       <c r="G50">
         <v>95.40000000000001</v>
@@ -5387,28 +5387,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M50">
-        <v>19.8896736</v>
+        <v>20.3040418</v>
       </c>
       <c r="N50">
-        <v>64.31032639999999</v>
+        <v>63.89595819999999</v>
       </c>
       <c r="O50">
-        <v>12.218962016</v>
+        <v>12.140232058</v>
       </c>
       <c r="P50">
-        <v>52.09136438399999</v>
+        <v>51.75572614199999</v>
       </c>
       <c r="Q50">
-        <v>120.891364384</v>
+        <v>120.555726142</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.122540378292161</v>
+        <v>0.1238815070035117</v>
       </c>
       <c r="T50">
-        <v>1.405526978528609</v>
+        <v>1.430090221861946</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.233352527212915</v>
+        <v>4.146957577677957</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08612038857179097</v>
+        <v>0.0860471404316582</v>
       </c>
       <c r="C51">
-        <v>394.0149124262524</v>
+        <v>388.0286962552288</v>
       </c>
       <c r="D51">
-        <v>649.8959124262524</v>
+        <v>651.0786962552288</v>
       </c>
       <c r="E51">
-        <v>-137.719</v>
+        <v>-130.55</v>
       </c>
       <c r="F51">
-        <v>351.281</v>
+        <v>358.45</v>
       </c>
       <c r="G51">
         <v>95.40000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M51">
-        <v>20.3040418</v>
+        <v>20.71841</v>
       </c>
       <c r="N51">
-        <v>63.89595819999999</v>
+        <v>63.48158999999998</v>
       </c>
       <c r="O51">
-        <v>12.140232058</v>
+        <v>12.0615021</v>
       </c>
       <c r="P51">
-        <v>51.75572614199999</v>
+        <v>51.42008789999998</v>
       </c>
       <c r="Q51">
-        <v>120.555726142</v>
+        <v>120.2200879</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1238815070035117</v>
+        <v>0.1252762808633164</v>
       </c>
       <c r="T51">
-        <v>1.430090221861946</v>
+        <v>1.455635994928617</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.146957577677957</v>
+        <v>4.064018426124397</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0860471404316582</v>
+        <v>0.08741974229152544</v>
       </c>
       <c r="C52">
-        <v>388.0286962552288</v>
+        <v>359.3873905609713</v>
       </c>
       <c r="D52">
-        <v>651.0786962552288</v>
+        <v>629.6063905609712</v>
       </c>
       <c r="E52">
-        <v>-130.55</v>
+        <v>-123.381</v>
       </c>
       <c r="F52">
-        <v>358.45</v>
+        <v>365.619</v>
       </c>
       <c r="G52">
         <v>95.40000000000001</v>
@@ -5551,45 +5551,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M52">
-        <v>20.71841</v>
+        <v>22.4124447</v>
       </c>
       <c r="N52">
-        <v>63.48158999999998</v>
+        <v>61.78755529999999</v>
       </c>
       <c r="O52">
-        <v>12.0615021</v>
+        <v>11.739635507</v>
       </c>
       <c r="P52">
-        <v>51.42008789999998</v>
+        <v>50.04791979299999</v>
       </c>
       <c r="Q52">
-        <v>120.2200879</v>
+        <v>118.847919793</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1252762808633164</v>
+        <v>0.1267279842684193</v>
       </c>
       <c r="T52">
-        <v>1.455635994928617</v>
+        <v>1.482224452610253</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.19</v>
       </c>
       <c r="W52">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.064018426124397</v>
+        <v>3.756841394459749</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08741974229152544</v>
+        <v>0.08737484415139268</v>
       </c>
       <c r="C53">
-        <v>359.3873905609713</v>
+        <v>352.8983247021299</v>
       </c>
       <c r="D53">
-        <v>629.6063905609712</v>
+        <v>630.2863247021299</v>
       </c>
       <c r="E53">
-        <v>-123.381</v>
+        <v>-116.212</v>
       </c>
       <c r="F53">
-        <v>365.619</v>
+        <v>372.788</v>
       </c>
       <c r="G53">
         <v>95.40000000000001</v>
@@ -5633,28 +5633,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M53">
-        <v>22.4124447</v>
+        <v>22.8519044</v>
       </c>
       <c r="N53">
-        <v>61.78755529999999</v>
+        <v>61.34809559999999</v>
       </c>
       <c r="O53">
-        <v>11.739635507</v>
+        <v>11.656138164</v>
       </c>
       <c r="P53">
-        <v>50.04791979299999</v>
+        <v>49.69195743599999</v>
       </c>
       <c r="Q53">
-        <v>118.847919793</v>
+        <v>118.491957436</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1267279842684193</v>
+        <v>0.1282401753154014</v>
       </c>
       <c r="T53">
-        <v>1.482224452610253</v>
+        <v>1.509920762695292</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.756841394459749</v>
+        <v>3.684594444566291</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08737484415139268</v>
+        <v>0.08732994601125992</v>
       </c>
       <c r="C54">
-        <v>352.8983247021299</v>
+        <v>346.4107290006708</v>
       </c>
       <c r="D54">
-        <v>630.2863247021299</v>
+        <v>630.9677290006708</v>
       </c>
       <c r="E54">
-        <v>-116.212</v>
+        <v>-109.043</v>
       </c>
       <c r="F54">
-        <v>372.788</v>
+        <v>379.957</v>
       </c>
       <c r="G54">
         <v>95.40000000000001</v>
@@ -5715,28 +5715,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M54">
-        <v>22.8519044</v>
+        <v>23.2913641</v>
       </c>
       <c r="N54">
-        <v>61.34809559999999</v>
+        <v>60.90863589999999</v>
       </c>
       <c r="O54">
-        <v>11.656138164</v>
+        <v>11.572640821</v>
       </c>
       <c r="P54">
-        <v>49.69195743599999</v>
+        <v>49.33599507899999</v>
       </c>
       <c r="Q54">
-        <v>118.491957436</v>
+        <v>118.135995079</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1282401753154014</v>
+        <v>0.1298167149175743</v>
       </c>
       <c r="T54">
-        <v>1.509920762695292</v>
+        <v>1.538795639166927</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.684594444566291</v>
+        <v>3.615073794668815</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08732994601125992</v>
+        <v>0.08728504787112715</v>
       </c>
       <c r="C55">
-        <v>346.4107290006708</v>
+        <v>339.9246082299277</v>
       </c>
       <c r="D55">
-        <v>630.9677290006708</v>
+        <v>631.6506082299278</v>
       </c>
       <c r="E55">
-        <v>-109.043</v>
+        <v>-101.874</v>
       </c>
       <c r="F55">
-        <v>379.957</v>
+        <v>387.126</v>
       </c>
       <c r="G55">
         <v>95.40000000000001</v>
@@ -5797,28 +5797,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M55">
-        <v>23.2913641</v>
+        <v>23.7308238</v>
       </c>
       <c r="N55">
-        <v>60.90863589999999</v>
+        <v>60.46917619999999</v>
       </c>
       <c r="O55">
-        <v>11.572640821</v>
+        <v>11.489143478</v>
       </c>
       <c r="P55">
-        <v>49.33599507899999</v>
+        <v>48.98003272199999</v>
       </c>
       <c r="Q55">
-        <v>118.135995079</v>
+        <v>117.780032722</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1298167149175743</v>
+        <v>0.1314617997198416</v>
       </c>
       <c r="T55">
-        <v>1.538795639166927</v>
+        <v>1.568925945050373</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.615073794668815</v>
+        <v>3.548127983656428</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08728504787112715</v>
+        <v>0.0884875497309944</v>
       </c>
       <c r="C56">
-        <v>339.9246082299277</v>
+        <v>314.9621055348956</v>
       </c>
       <c r="D56">
-        <v>631.6506082299278</v>
+        <v>613.8571055348956</v>
       </c>
       <c r="E56">
-        <v>-101.874</v>
+        <v>-94.70499999999998</v>
       </c>
       <c r="F56">
-        <v>387.126</v>
+        <v>394.295</v>
       </c>
       <c r="G56">
         <v>95.40000000000001</v>
@@ -5879,45 +5879,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M56">
-        <v>23.7308238</v>
+        <v>25.2743095</v>
       </c>
       <c r="N56">
-        <v>60.46917619999999</v>
+        <v>58.92569049999999</v>
       </c>
       <c r="O56">
-        <v>11.489143478</v>
+        <v>11.195881195</v>
       </c>
       <c r="P56">
-        <v>48.98003272199999</v>
+        <v>47.72980930499999</v>
       </c>
       <c r="Q56">
-        <v>117.780032722</v>
+        <v>116.529809305</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1314617997198416</v>
+        <v>0.1331799994022098</v>
       </c>
       <c r="T56">
-        <v>1.568925945050373</v>
+        <v>1.60039537563975</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.548127983656428</v>
+        <v>3.331446107360519</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0884875497309944</v>
+        <v>0.08846533159086162</v>
       </c>
       <c r="C57">
-        <v>314.9621055348956</v>
+        <v>308.1127740499107</v>
       </c>
       <c r="D57">
-        <v>613.8571055348956</v>
+        <v>614.1767740499107</v>
       </c>
       <c r="E57">
-        <v>-94.70499999999998</v>
+        <v>-87.536</v>
       </c>
       <c r="F57">
-        <v>394.295</v>
+        <v>401.464</v>
       </c>
       <c r="G57">
         <v>95.40000000000001</v>
@@ -5961,28 +5961,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M57">
-        <v>25.2743095</v>
+        <v>25.7338424</v>
       </c>
       <c r="N57">
-        <v>58.92569049999999</v>
+        <v>58.46615759999999</v>
       </c>
       <c r="O57">
-        <v>11.195881195</v>
+        <v>11.108569944</v>
       </c>
       <c r="P57">
-        <v>47.72980930499999</v>
+        <v>47.35758765599999</v>
       </c>
       <c r="Q57">
-        <v>116.529809305</v>
+        <v>116.157587656</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1331799994022098</v>
+        <v>0.1349762990701401</v>
       </c>
       <c r="T57">
-        <v>1.60039537563975</v>
+        <v>1.63329523489228</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.331446107360519</v>
+        <v>3.27195599830051</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08846533159086162</v>
+        <v>0.08844311345072886</v>
       </c>
       <c r="C58">
-        <v>308.1127740499107</v>
+        <v>301.2637756756807</v>
       </c>
       <c r="D58">
-        <v>614.1767740499107</v>
+        <v>614.4967756756807</v>
       </c>
       <c r="E58">
-        <v>-87.536</v>
+        <v>-80.36699999999996</v>
       </c>
       <c r="F58">
-        <v>401.464</v>
+        <v>408.633</v>
       </c>
       <c r="G58">
         <v>95.40000000000001</v>
@@ -6043,28 +6043,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M58">
-        <v>25.7338424</v>
+        <v>26.1933753</v>
       </c>
       <c r="N58">
-        <v>58.46615759999999</v>
+        <v>58.00662469999999</v>
       </c>
       <c r="O58">
-        <v>11.108569944</v>
+        <v>11.021258693</v>
       </c>
       <c r="P58">
-        <v>47.35758765599999</v>
+        <v>46.98536600699999</v>
       </c>
       <c r="Q58">
-        <v>116.157587656</v>
+        <v>115.785366007</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1349762990701401</v>
+        <v>0.1368561475598346</v>
       </c>
       <c r="T58">
-        <v>1.63329523489228</v>
+        <v>1.667725320156556</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.27195599830051</v>
+        <v>3.21455326148822</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08844311345072886</v>
+        <v>0.0884208953105961</v>
       </c>
       <c r="C59">
-        <v>301.2637756756807</v>
+        <v>294.4151109331546</v>
       </c>
       <c r="D59">
-        <v>614.4967756756807</v>
+        <v>614.8171109331546</v>
       </c>
       <c r="E59">
-        <v>-80.36699999999996</v>
+        <v>-73.19799999999998</v>
       </c>
       <c r="F59">
-        <v>408.633</v>
+        <v>415.802</v>
       </c>
       <c r="G59">
         <v>95.40000000000001</v>
@@ -6125,28 +6125,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M59">
-        <v>26.1933753</v>
+        <v>26.6529082</v>
       </c>
       <c r="N59">
-        <v>58.00662469999999</v>
+        <v>57.54709179999999</v>
       </c>
       <c r="O59">
-        <v>11.021258693</v>
+        <v>10.933947442</v>
       </c>
       <c r="P59">
-        <v>46.98536600699999</v>
+        <v>46.61314435799999</v>
       </c>
       <c r="Q59">
-        <v>115.785366007</v>
+        <v>115.413144358</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1368561475598346</v>
+        <v>0.1388255126442764</v>
       </c>
       <c r="T59">
-        <v>1.667725320156556</v>
+        <v>1.70379493329056</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.21455326148822</v>
+        <v>3.159129929393595</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0884208953105961</v>
+        <v>0.08839867717046333</v>
       </c>
       <c r="C60">
-        <v>294.4151109331546</v>
+        <v>287.5667803443684</v>
       </c>
       <c r="D60">
-        <v>614.8171109331546</v>
+        <v>615.1377803443684</v>
       </c>
       <c r="E60">
-        <v>-73.19800000000004</v>
+        <v>-66.02900000000005</v>
       </c>
       <c r="F60">
-        <v>415.802</v>
+        <v>422.9709999999999</v>
       </c>
       <c r="G60">
         <v>95.40000000000001</v>
@@ -6207,28 +6207,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M60">
-        <v>26.6529082</v>
+        <v>27.1124411</v>
       </c>
       <c r="N60">
-        <v>57.54709179999999</v>
+        <v>57.08755889999999</v>
       </c>
       <c r="O60">
-        <v>10.933947442</v>
+        <v>10.846636191</v>
       </c>
       <c r="P60">
-        <v>46.61314435799999</v>
+        <v>46.24092270899999</v>
       </c>
       <c r="Q60">
-        <v>115.413144358</v>
+        <v>115.040922709</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1388255126442764</v>
+        <v>0.1408909443182032</v>
       </c>
       <c r="T60">
-        <v>1.703794933290559</v>
+        <v>1.741624039748172</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.159129929393596</v>
+        <v>3.105585354319128</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08839867717046333</v>
+        <v>0.08837645903033056</v>
       </c>
       <c r="C61">
-        <v>287.5667803443684</v>
+        <v>280.7187844324471</v>
       </c>
       <c r="D61">
-        <v>615.1377803443684</v>
+        <v>615.4587844324471</v>
       </c>
       <c r="E61">
-        <v>-66.02900000000005</v>
+        <v>-58.86000000000001</v>
       </c>
       <c r="F61">
-        <v>422.9709999999999</v>
+        <v>430.14</v>
       </c>
       <c r="G61">
         <v>95.40000000000001</v>
@@ -6289,28 +6289,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M61">
-        <v>27.1124411</v>
+        <v>27.571974</v>
       </c>
       <c r="N61">
-        <v>57.08755889999999</v>
+        <v>56.62802599999999</v>
       </c>
       <c r="O61">
-        <v>10.846636191</v>
+        <v>10.75932494</v>
       </c>
       <c r="P61">
-        <v>46.24092270899999</v>
+        <v>45.86870105999999</v>
       </c>
       <c r="Q61">
-        <v>115.040922709</v>
+        <v>114.66870106</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1408909443182032</v>
+        <v>0.1430596475758264</v>
       </c>
       <c r="T61">
-        <v>1.741624039748172</v>
+        <v>1.781344601528666</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.105585354319128</v>
+        <v>3.053825598413809</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08837645903033056</v>
+        <v>0.0883542408901978</v>
       </c>
       <c r="C62">
-        <v>280.7187844324471</v>
+        <v>273.8711237216085</v>
       </c>
       <c r="D62">
-        <v>615.4587844324471</v>
+        <v>615.7801237216084</v>
       </c>
       <c r="E62">
-        <v>-58.86000000000001</v>
+        <v>-51.69100000000003</v>
       </c>
       <c r="F62">
-        <v>430.14</v>
+        <v>437.309</v>
       </c>
       <c r="G62">
         <v>95.40000000000001</v>
@@ -6371,28 +6371,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M62">
-        <v>27.571974</v>
+        <v>28.0315069</v>
       </c>
       <c r="N62">
-        <v>56.62802599999999</v>
+        <v>56.16849309999999</v>
       </c>
       <c r="O62">
-        <v>10.75932494</v>
+        <v>10.672013689</v>
       </c>
       <c r="P62">
-        <v>45.86870105999999</v>
+        <v>45.496479411</v>
       </c>
       <c r="Q62">
-        <v>114.66870106</v>
+        <v>114.296479411</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1430596475758264</v>
+        <v>0.1453395663851226</v>
       </c>
       <c r="T62">
-        <v>1.781344601528666</v>
+        <v>1.823102115195339</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.053825598413809</v>
+        <v>3.003762883685714</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0883542408901978</v>
+        <v>0.09224918275006505</v>
       </c>
       <c r="C63">
-        <v>273.8711237216085</v>
+        <v>215.0666020965446</v>
       </c>
       <c r="D63">
-        <v>615.7801237216084</v>
+        <v>564.1446020965446</v>
       </c>
       <c r="E63">
-        <v>-51.69100000000003</v>
+        <v>-44.52199999999999</v>
       </c>
       <c r="F63">
-        <v>437.309</v>
+        <v>444.478</v>
       </c>
       <c r="G63">
         <v>95.40000000000001</v>
@@ -6453,45 +6453,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M63">
-        <v>28.0315069</v>
+        <v>31.9579682</v>
       </c>
       <c r="N63">
-        <v>56.16849309999999</v>
+        <v>52.24203179999999</v>
       </c>
       <c r="O63">
-        <v>10.672013689</v>
+        <v>9.925986041999998</v>
       </c>
       <c r="P63">
-        <v>45.496479411</v>
+        <v>42.31604575799999</v>
       </c>
       <c r="Q63">
-        <v>114.296479411</v>
+        <v>111.116045758</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1453395663851226</v>
+        <v>0.1477394809212238</v>
       </c>
       <c r="T63">
-        <v>1.823102115195339</v>
+        <v>1.867057392739206</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.19</v>
       </c>
       <c r="W63">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.003762883685714</v>
+        <v>2.634710676005992</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09224918275006505</v>
+        <v>0.09229014460993229</v>
       </c>
       <c r="C64">
-        <v>215.0666020965446</v>
+        <v>207.4005416479308</v>
       </c>
       <c r="D64">
-        <v>564.1446020965446</v>
+        <v>563.6475416479308</v>
       </c>
       <c r="E64">
-        <v>-44.52199999999999</v>
+        <v>-37.35300000000001</v>
       </c>
       <c r="F64">
-        <v>444.478</v>
+        <v>451.647</v>
       </c>
       <c r="G64">
         <v>95.40000000000001</v>
@@ -6535,28 +6535,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M64">
-        <v>31.9579682</v>
+        <v>32.4734193</v>
       </c>
       <c r="N64">
-        <v>52.24203179999999</v>
+        <v>51.72658069999999</v>
       </c>
       <c r="O64">
-        <v>9.925986041999998</v>
+        <v>9.828050332999997</v>
       </c>
       <c r="P64">
-        <v>42.31604575799999</v>
+        <v>41.89853036699999</v>
       </c>
       <c r="Q64">
-        <v>111.116045758</v>
+        <v>110.698530367</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1477394809212238</v>
+        <v>0.1502691205673845</v>
       </c>
       <c r="T64">
-        <v>1.867057392739206</v>
+        <v>1.913388631231389</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.634710676005992</v>
+        <v>2.592889871624944</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09229014460993229</v>
+        <v>0.09233110646979953</v>
       </c>
       <c r="C65">
-        <v>207.4005416479308</v>
+        <v>199.7353563351984</v>
       </c>
       <c r="D65">
-        <v>563.6475416479308</v>
+        <v>563.1513563351984</v>
       </c>
       <c r="E65">
-        <v>-37.35300000000001</v>
+        <v>-30.18400000000003</v>
       </c>
       <c r="F65">
-        <v>451.647</v>
+        <v>458.816</v>
       </c>
       <c r="G65">
         <v>95.40000000000001</v>
@@ -6617,28 +6617,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M65">
-        <v>32.4734193</v>
+        <v>32.9888704</v>
       </c>
       <c r="N65">
-        <v>51.72658069999999</v>
+        <v>51.21112959999999</v>
       </c>
       <c r="O65">
-        <v>9.828050332999997</v>
+        <v>9.730114623999997</v>
       </c>
       <c r="P65">
-        <v>41.89853036699999</v>
+        <v>41.48101497599999</v>
       </c>
       <c r="Q65">
-        <v>110.698530367</v>
+        <v>110.281014976</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1502691205673845</v>
+        <v>0.1529392957494431</v>
       </c>
       <c r="T65">
-        <v>1.913388631231389</v>
+        <v>1.962293827417583</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.592889871624944</v>
+        <v>2.552375967380804</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09233110646979953</v>
+        <v>0.09237206832966675</v>
       </c>
       <c r="C66">
-        <v>199.7353563351984</v>
+        <v>192.0710438492047</v>
       </c>
       <c r="D66">
-        <v>563.1513563351984</v>
+        <v>562.6560438492047</v>
       </c>
       <c r="E66">
-        <v>-30.18400000000003</v>
+        <v>-23.01499999999999</v>
       </c>
       <c r="F66">
-        <v>458.816</v>
+        <v>465.985</v>
       </c>
       <c r="G66">
         <v>95.40000000000001</v>
@@ -6699,28 +6699,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M66">
-        <v>32.9888704</v>
+        <v>33.5043215</v>
       </c>
       <c r="N66">
-        <v>51.21112959999999</v>
+        <v>50.69567849999999</v>
       </c>
       <c r="O66">
-        <v>9.730114623999997</v>
+        <v>9.632178914999997</v>
       </c>
       <c r="P66">
-        <v>41.48101497599999</v>
+        <v>41.06349958499999</v>
       </c>
       <c r="Q66">
-        <v>110.281014976</v>
+        <v>109.863499585</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1529392957494431</v>
+        <v>0.1557620523704764</v>
       </c>
       <c r="T66">
-        <v>1.962293827417583</v>
+        <v>2.013993606242988</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.552375967380804</v>
+        <v>2.513108644805715</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09237206832966675</v>
+        <v>0.09449797018953399</v>
       </c>
       <c r="C67">
-        <v>192.0710438492047</v>
+        <v>160.3393870191745</v>
       </c>
       <c r="D67">
-        <v>562.6560438492047</v>
+        <v>538.0933870191745</v>
       </c>
       <c r="E67">
-        <v>-23.01499999999999</v>
+        <v>-15.846</v>
       </c>
       <c r="F67">
-        <v>465.985</v>
+        <v>473.154</v>
       </c>
       <c r="G67">
         <v>95.40000000000001</v>
@@ -6781,45 +6781,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M67">
-        <v>33.5043215</v>
+        <v>35.8650732</v>
       </c>
       <c r="N67">
-        <v>50.69567849999999</v>
+        <v>48.33492679999998</v>
       </c>
       <c r="O67">
-        <v>9.632178914999997</v>
+        <v>9.183636091999997</v>
       </c>
       <c r="P67">
-        <v>41.06349958499999</v>
+        <v>39.15129070799999</v>
       </c>
       <c r="Q67">
-        <v>109.863499585</v>
+        <v>107.951290708</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1557620523704764</v>
+        <v>0.1587508534986294</v>
       </c>
       <c r="T67">
-        <v>2.013993606242988</v>
+        <v>2.06873454852871</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.19</v>
       </c>
       <c r="W67">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.513108644805715</v>
+        <v>2.347687945050673</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09449797018953399</v>
+        <v>0.09457052204940122</v>
       </c>
       <c r="C68">
-        <v>160.3393870191745</v>
+        <v>152.3699101251408</v>
       </c>
       <c r="D68">
-        <v>538.0933870191745</v>
+        <v>537.2929101251409</v>
       </c>
       <c r="E68">
-        <v>-15.846</v>
+        <v>-8.676999999999964</v>
       </c>
       <c r="F68">
-        <v>473.154</v>
+        <v>480.323</v>
       </c>
       <c r="G68">
         <v>95.40000000000001</v>
@@ -6863,28 +6863,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M68">
-        <v>35.8650732</v>
+        <v>36.40848340000001</v>
       </c>
       <c r="N68">
-        <v>48.33492679999998</v>
+        <v>47.79151659999998</v>
       </c>
       <c r="O68">
-        <v>9.183636091999997</v>
+        <v>9.080388153999996</v>
       </c>
       <c r="P68">
-        <v>39.15129070799999</v>
+        <v>38.71112844599998</v>
       </c>
       <c r="Q68">
-        <v>107.951290708</v>
+        <v>107.511128446</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1587508534986294</v>
+        <v>0.1619207940890946</v>
       </c>
       <c r="T68">
-        <v>2.06873454852871</v>
+        <v>2.126793123680234</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.347687945050673</v>
+        <v>2.312647826467827</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09457052204940122</v>
+        <v>0.09464307390926846</v>
       </c>
       <c r="C69">
-        <v>152.3699101251408</v>
+        <v>144.4028112995945</v>
       </c>
       <c r="D69">
-        <v>537.2929101251409</v>
+        <v>536.4948112995945</v>
       </c>
       <c r="E69">
-        <v>-8.676999999999964</v>
+        <v>-1.507999999999981</v>
       </c>
       <c r="F69">
-        <v>480.323</v>
+        <v>487.492</v>
       </c>
       <c r="G69">
         <v>95.40000000000001</v>
@@ -6945,28 +6945,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M69">
-        <v>36.40848340000001</v>
+        <v>36.95189360000001</v>
       </c>
       <c r="N69">
-        <v>47.79151659999998</v>
+        <v>47.24810639999998</v>
       </c>
       <c r="O69">
-        <v>9.080388153999996</v>
+        <v>8.977140215999997</v>
       </c>
       <c r="P69">
-        <v>38.71112844599998</v>
+        <v>38.27096618399999</v>
       </c>
       <c r="Q69">
-        <v>107.511128446</v>
+        <v>107.070966184</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1619207940890946</v>
+        <v>0.1652888559664639</v>
       </c>
       <c r="T69">
-        <v>2.126793123680234</v>
+        <v>2.188480359778728</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.312647826467827</v>
+        <v>2.278638299608007</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09464307390926846</v>
+        <v>0.09471562576913571</v>
       </c>
       <c r="C70">
-        <v>144.4028112995945</v>
+        <v>136.4380799610521</v>
       </c>
       <c r="D70">
-        <v>536.4948112995945</v>
+        <v>535.6990799610521</v>
       </c>
       <c r="E70">
-        <v>-1.507999999999981</v>
+        <v>5.661000000000001</v>
       </c>
       <c r="F70">
-        <v>487.492</v>
+        <v>494.661</v>
       </c>
       <c r="G70">
         <v>95.40000000000001</v>
@@ -7027,28 +7027,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M70">
-        <v>36.95189360000001</v>
+        <v>37.4953038</v>
       </c>
       <c r="N70">
-        <v>47.24810639999998</v>
+        <v>46.70469619999999</v>
       </c>
       <c r="O70">
-        <v>8.977140215999997</v>
+        <v>8.873892277999998</v>
       </c>
       <c r="P70">
-        <v>38.27096618399999</v>
+        <v>37.83080392199999</v>
       </c>
       <c r="Q70">
-        <v>107.070966184</v>
+        <v>106.630803922</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1652888559664639</v>
+        <v>0.1688742121585023</v>
       </c>
       <c r="T70">
-        <v>2.188480359778728</v>
+        <v>2.254147417560997</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.278638299608007</v>
+        <v>2.245614556135427</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09471562576913571</v>
+        <v>0.09478817762900295</v>
       </c>
       <c r="C71">
-        <v>136.4380799610521</v>
+        <v>128.4757055907156</v>
       </c>
       <c r="D71">
-        <v>535.6990799610521</v>
+        <v>534.9057055907157</v>
       </c>
       <c r="E71">
-        <v>5.661000000000001</v>
+        <v>12.83000000000004</v>
       </c>
       <c r="F71">
-        <v>494.661</v>
+        <v>501.83</v>
       </c>
       <c r="G71">
         <v>95.40000000000001</v>
@@ -7109,28 +7109,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M71">
-        <v>37.4953038</v>
+        <v>38.03871400000001</v>
       </c>
       <c r="N71">
-        <v>46.70469619999999</v>
+        <v>46.16128599999998</v>
       </c>
       <c r="O71">
-        <v>8.873892277999998</v>
+        <v>8.770644339999997</v>
       </c>
       <c r="P71">
-        <v>37.83080392199999</v>
+        <v>37.39064165999999</v>
       </c>
       <c r="Q71">
-        <v>106.630803922</v>
+        <v>106.19064166</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1688742121585023</v>
+        <v>0.1726985920966765</v>
       </c>
       <c r="T71">
-        <v>2.254147417560997</v>
+        <v>2.324192279195416</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.245614556135427</v>
+        <v>2.213534348190635</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09478817762900295</v>
+        <v>0.0948607294888702</v>
       </c>
       <c r="C72">
-        <v>128.4757055907156</v>
+        <v>120.515677732008</v>
       </c>
       <c r="D72">
-        <v>534.9057055907157</v>
+        <v>534.1146777320081</v>
       </c>
       <c r="E72">
-        <v>12.83000000000004</v>
+        <v>19.99900000000002</v>
       </c>
       <c r="F72">
-        <v>501.83</v>
+        <v>508.999</v>
       </c>
       <c r="G72">
         <v>95.40000000000001</v>
@@ -7191,28 +7191,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M72">
-        <v>38.03871400000001</v>
+        <v>38.5821242</v>
       </c>
       <c r="N72">
-        <v>46.16128599999998</v>
+        <v>45.61787579999999</v>
       </c>
       <c r="O72">
-        <v>8.770644339999997</v>
+        <v>8.667396401999998</v>
       </c>
       <c r="P72">
-        <v>37.39064165999999</v>
+        <v>36.95047939799998</v>
       </c>
       <c r="Q72">
-        <v>106.19064166</v>
+        <v>105.750479398</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1726985920966765</v>
+        <v>0.1767867223754145</v>
       </c>
       <c r="T72">
-        <v>2.324192279195416</v>
+        <v>2.399067820942554</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.213534348190635</v>
+        <v>2.182357808075274</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09486072948887017</v>
+        <v>0.09493328134873742</v>
       </c>
       <c r="C73">
-        <v>120.5156777320084</v>
+        <v>112.5579859901154</v>
       </c>
       <c r="D73">
-        <v>534.1146777320084</v>
+        <v>533.3259859901154</v>
       </c>
       <c r="E73">
-        <v>19.99899999999997</v>
+        <v>27.16800000000001</v>
       </c>
       <c r="F73">
-        <v>508.999</v>
+        <v>516.168</v>
       </c>
       <c r="G73">
         <v>95.40000000000001</v>
@@ -7273,28 +7273,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M73">
-        <v>38.5821242</v>
+        <v>39.12553440000001</v>
       </c>
       <c r="N73">
-        <v>45.61787579999999</v>
+        <v>45.07446559999998</v>
       </c>
       <c r="O73">
-        <v>8.667396401999998</v>
+        <v>8.564148463999997</v>
       </c>
       <c r="P73">
-        <v>36.95047939799998</v>
+        <v>36.51031713599998</v>
       </c>
       <c r="Q73">
-        <v>105.750479398</v>
+        <v>105.310317136</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1767867223754144</v>
+        <v>0.1811668619597765</v>
       </c>
       <c r="T73">
-        <v>2.399067820942553</v>
+        <v>2.47929161567163</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.182357808075274</v>
+        <v>2.152047282963117</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09493328134873742</v>
+        <v>0.09500583320860465</v>
       </c>
       <c r="C74">
-        <v>112.5579859901154</v>
+        <v>104.6026200315295</v>
       </c>
       <c r="D74">
-        <v>533.3259859901154</v>
+        <v>532.5396200315295</v>
       </c>
       <c r="E74">
-        <v>27.16800000000001</v>
+        <v>34.33699999999999</v>
       </c>
       <c r="F74">
-        <v>516.168</v>
+        <v>523.337</v>
       </c>
       <c r="G74">
         <v>95.40000000000001</v>
@@ -7355,28 +7355,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M74">
-        <v>39.12553440000001</v>
+        <v>39.6689446</v>
       </c>
       <c r="N74">
-        <v>45.07446559999998</v>
+        <v>44.53105539999999</v>
       </c>
       <c r="O74">
-        <v>8.564148463999997</v>
+        <v>8.460900525999998</v>
       </c>
       <c r="P74">
-        <v>36.51031713599998</v>
+        <v>36.07015487399999</v>
       </c>
       <c r="Q74">
-        <v>105.310317136</v>
+        <v>104.870154874</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1811668619597765</v>
+        <v>0.1858714563281653</v>
       </c>
       <c r="T74">
-        <v>2.47929161567163</v>
+        <v>2.565457913713971</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.152047282963117</v>
+        <v>2.122567183196499</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09500583320860465</v>
+        <v>0.09507838506847188</v>
       </c>
       <c r="C75">
-        <v>104.6026200315295</v>
+        <v>96.64956958359789</v>
       </c>
       <c r="D75">
-        <v>532.5396200315295</v>
+        <v>531.7555695835979</v>
       </c>
       <c r="E75">
-        <v>34.33699999999999</v>
+        <v>41.50599999999997</v>
       </c>
       <c r="F75">
-        <v>523.337</v>
+        <v>530.506</v>
       </c>
       <c r="G75">
         <v>95.40000000000001</v>
@@ -7437,28 +7437,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M75">
-        <v>39.6689446</v>
+        <v>40.2123548</v>
       </c>
       <c r="N75">
-        <v>44.53105539999999</v>
+        <v>43.98764519999999</v>
       </c>
       <c r="O75">
-        <v>8.460900525999998</v>
+        <v>8.357652587999999</v>
       </c>
       <c r="P75">
-        <v>36.07015487399999</v>
+        <v>35.62999261199999</v>
       </c>
       <c r="Q75">
-        <v>104.870154874</v>
+        <v>104.429992612</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1858714563281653</v>
+        <v>0.1909379425710457</v>
       </c>
       <c r="T75">
-        <v>2.565457913713971</v>
+        <v>2.658252388528799</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.122567183196499</v>
+        <v>2.093883842883034</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09507838506847188</v>
+        <v>0.09515093692833912</v>
       </c>
       <c r="C76">
-        <v>96.64956958359789</v>
+        <v>88.69882443407687</v>
       </c>
       <c r="D76">
-        <v>531.7555695835979</v>
+        <v>530.9738244340768</v>
       </c>
       <c r="E76">
-        <v>41.50599999999997</v>
+        <v>48.67499999999995</v>
       </c>
       <c r="F76">
-        <v>530.506</v>
+        <v>537.675</v>
       </c>
       <c r="G76">
         <v>95.40000000000001</v>
@@ -7519,28 +7519,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M76">
-        <v>40.2123548</v>
+        <v>40.755765</v>
       </c>
       <c r="N76">
-        <v>43.98764519999999</v>
+        <v>43.44423499999999</v>
       </c>
       <c r="O76">
-        <v>8.357652587999999</v>
+        <v>8.254404649999998</v>
       </c>
       <c r="P76">
-        <v>35.62999261199999</v>
+        <v>35.18983034999999</v>
       </c>
       <c r="Q76">
-        <v>104.429992612</v>
+        <v>103.98983035</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1909379425710457</v>
+        <v>0.1964097477133565</v>
       </c>
       <c r="T76">
-        <v>2.658252388528799</v>
+        <v>2.758470421328815</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.093883842883034</v>
+        <v>2.065965391644593</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09515093692833912</v>
+        <v>0.09522348878820637</v>
       </c>
       <c r="C77">
-        <v>88.69882443407687</v>
+        <v>80.75037443068675</v>
       </c>
       <c r="D77">
-        <v>530.9738244340768</v>
+        <v>530.1943744306867</v>
       </c>
       <c r="E77">
-        <v>48.67499999999995</v>
+        <v>55.84399999999994</v>
       </c>
       <c r="F77">
-        <v>537.675</v>
+        <v>544.8439999999999</v>
       </c>
       <c r="G77">
         <v>95.40000000000001</v>
@@ -7601,28 +7601,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M77">
-        <v>40.755765</v>
+        <v>41.2991752</v>
       </c>
       <c r="N77">
-        <v>43.44423499999999</v>
+        <v>42.90082479999999</v>
       </c>
       <c r="O77">
-        <v>8.254404649999998</v>
+        <v>8.151156711999997</v>
       </c>
       <c r="P77">
-        <v>35.18983034999999</v>
+        <v>34.74966808799999</v>
       </c>
       <c r="Q77">
-        <v>103.98983035</v>
+        <v>103.549668088</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1964097477133565</v>
+        <v>0.2023375366175265</v>
       </c>
       <c r="T77">
-        <v>2.758470421328815</v>
+        <v>2.867039956862165</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.065965391644593</v>
+        <v>2.038781636491374</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09522348878820637</v>
+        <v>0.09529604064807361</v>
       </c>
       <c r="C78">
-        <v>80.75037443068675</v>
+        <v>72.80420948067388</v>
       </c>
       <c r="D78">
-        <v>530.1943744306867</v>
+        <v>529.4172094806739</v>
       </c>
       <c r="E78">
-        <v>55.84399999999994</v>
+        <v>63.01300000000003</v>
       </c>
       <c r="F78">
-        <v>544.8439999999999</v>
+        <v>552.013</v>
       </c>
       <c r="G78">
         <v>95.40000000000001</v>
@@ -7683,28 +7683,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M78">
-        <v>41.2991752</v>
+        <v>41.8425854</v>
       </c>
       <c r="N78">
-        <v>42.90082479999999</v>
+        <v>42.35741459999998</v>
       </c>
       <c r="O78">
-        <v>8.151156711999997</v>
+        <v>8.047908773999998</v>
       </c>
       <c r="P78">
-        <v>34.74966808799999</v>
+        <v>34.30950582599998</v>
       </c>
       <c r="Q78">
-        <v>103.549668088</v>
+        <v>103.109505826</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2023375366175265</v>
+        <v>0.208780785426407</v>
       </c>
       <c r="T78">
-        <v>2.867039956862165</v>
+        <v>2.985050321572328</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.038781636491374</v>
+        <v>2.012303952900577</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09529604064807361</v>
+        <v>0.1043401525079408</v>
       </c>
       <c r="C79">
-        <v>72.80420948067388</v>
+        <v>-16.15665914202032</v>
       </c>
       <c r="D79">
-        <v>529.4172094806739</v>
+        <v>447.6253408579797</v>
       </c>
       <c r="E79">
-        <v>63.01300000000003</v>
+        <v>70.18200000000002</v>
       </c>
       <c r="F79">
-        <v>552.013</v>
+        <v>559.182</v>
       </c>
       <c r="G79">
         <v>95.40000000000001</v>
@@ -7765,45 +7765,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M79">
-        <v>41.8425854</v>
+        <v>50.32638</v>
       </c>
       <c r="N79">
-        <v>42.35741459999998</v>
+        <v>33.87361999999999</v>
       </c>
       <c r="O79">
-        <v>8.047908773999998</v>
+        <v>6.435987799999998</v>
       </c>
       <c r="P79">
-        <v>34.30950582599998</v>
+        <v>27.43763219999999</v>
       </c>
       <c r="Q79">
-        <v>103.109505826</v>
+        <v>96.23763220000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.208780785426407</v>
+        <v>0.2158097841270038</v>
       </c>
       <c r="T79">
-        <v>2.985050321572328</v>
+        <v>3.113788901256142</v>
       </c>
       <c r="U79">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
         <v>0.19</v>
       </c>
       <c r="W79">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.012303952900577</v>
+        <v>1.673078810754916</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1043401525079408</v>
+        <v>0.1045277243678081</v>
       </c>
       <c r="C80">
-        <v>-16.15665914202032</v>
+        <v>-24.75534024429817</v>
       </c>
       <c r="D80">
-        <v>447.6253408579797</v>
+        <v>446.1956597557019</v>
       </c>
       <c r="E80">
-        <v>70.18200000000002</v>
+        <v>77.351</v>
       </c>
       <c r="F80">
-        <v>559.182</v>
+        <v>566.351</v>
       </c>
       <c r="G80">
         <v>95.40000000000001</v>
@@ -7847,28 +7847,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M80">
-        <v>50.32638</v>
+        <v>50.97159</v>
       </c>
       <c r="N80">
-        <v>33.87361999999999</v>
+        <v>33.22840999999999</v>
       </c>
       <c r="O80">
-        <v>6.435987799999998</v>
+        <v>6.313397899999998</v>
       </c>
       <c r="P80">
-        <v>27.43763219999999</v>
+        <v>26.91501209999999</v>
       </c>
       <c r="Q80">
-        <v>96.23763220000001</v>
+        <v>95.7150121</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2158097841270038</v>
+        <v>0.2235082112752766</v>
       </c>
       <c r="T80">
-        <v>3.113788901256142</v>
+        <v>3.254788298052701</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.673078810754916</v>
+        <v>1.65190059796055</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1045277243678081</v>
+        <v>0.1047152962276753</v>
       </c>
       <c r="C81">
-        <v>-24.75534024429817</v>
+        <v>-33.34491783830083</v>
       </c>
       <c r="D81">
-        <v>446.1956597557019</v>
+        <v>444.7750821616991</v>
       </c>
       <c r="E81">
-        <v>77.351</v>
+        <v>84.51999999999998</v>
       </c>
       <c r="F81">
-        <v>566.351</v>
+        <v>573.52</v>
       </c>
       <c r="G81">
         <v>95.40000000000001</v>
@@ -7929,28 +7929,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M81">
-        <v>50.97159</v>
+        <v>51.6168</v>
       </c>
       <c r="N81">
-        <v>33.22840999999999</v>
+        <v>32.58319999999999</v>
       </c>
       <c r="O81">
-        <v>6.313397899999998</v>
+        <v>6.190807999999999</v>
       </c>
       <c r="P81">
-        <v>26.91501209999999</v>
+        <v>26.39239199999999</v>
       </c>
       <c r="Q81">
-        <v>95.7150121</v>
+        <v>95.19239200000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2235082112752766</v>
+        <v>0.2319764811383766</v>
       </c>
       <c r="T81">
-        <v>3.254788298052701</v>
+        <v>3.409887634528915</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.65190059796055</v>
+        <v>1.631251840486043</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1047152962276753</v>
+        <v>0.1049028680875426</v>
       </c>
       <c r="C82">
-        <v>-33.34491783830083</v>
+        <v>-41.9254785980952</v>
       </c>
       <c r="D82">
-        <v>444.7750821616991</v>
+        <v>443.3635214019048</v>
       </c>
       <c r="E82">
-        <v>84.51999999999998</v>
+        <v>91.68899999999996</v>
       </c>
       <c r="F82">
-        <v>573.52</v>
+        <v>580.689</v>
       </c>
       <c r="G82">
         <v>95.40000000000001</v>
@@ -8011,28 +8011,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M82">
-        <v>51.6168</v>
+        <v>52.26201</v>
       </c>
       <c r="N82">
-        <v>32.58319999999999</v>
+        <v>31.93798999999999</v>
       </c>
       <c r="O82">
-        <v>6.190807999999999</v>
+        <v>6.068218099999998</v>
       </c>
       <c r="P82">
-        <v>26.39239199999999</v>
+        <v>25.86977189999999</v>
       </c>
       <c r="Q82">
-        <v>95.19239200000001</v>
+        <v>94.6697719</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2319764811383766</v>
+        <v>0.2413361478291714</v>
       </c>
       <c r="T82">
-        <v>3.409887634528915</v>
+        <v>3.581313216949994</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.631251840486043</v>
+        <v>1.611112928875104</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1049028680875426</v>
+        <v>0.1050904399474098</v>
       </c>
       <c r="C83">
-        <v>-41.9254785980952</v>
+        <v>-50.49710810093575</v>
       </c>
       <c r="D83">
-        <v>443.3635214019048</v>
+        <v>441.9608918990643</v>
       </c>
       <c r="E83">
-        <v>91.68899999999996</v>
+        <v>98.85800000000006</v>
       </c>
       <c r="F83">
-        <v>580.689</v>
+        <v>587.8580000000001</v>
       </c>
       <c r="G83">
         <v>95.40000000000001</v>
@@ -8093,28 +8093,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M83">
-        <v>52.26201</v>
+        <v>52.90722</v>
       </c>
       <c r="N83">
-        <v>31.93798999999999</v>
+        <v>31.29277999999999</v>
       </c>
       <c r="O83">
-        <v>6.068218099999998</v>
+        <v>5.945628199999997</v>
       </c>
       <c r="P83">
-        <v>25.86977189999999</v>
+        <v>25.34715179999999</v>
       </c>
       <c r="Q83">
-        <v>94.6697719</v>
+        <v>94.1471518</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2413361478291714</v>
+        <v>0.2517357774856099</v>
       </c>
       <c r="T83">
-        <v>3.581313216949994</v>
+        <v>3.771786086306748</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.611112928875104</v>
+        <v>1.591465210230286</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1050904399474098</v>
+        <v>0.105278011807277</v>
       </c>
       <c r="C84">
-        <v>-50.49710810093575</v>
+        <v>-59.05989084456064</v>
       </c>
       <c r="D84">
-        <v>441.9608918990643</v>
+        <v>440.5671091554394</v>
       </c>
       <c r="E84">
-        <v>98.85800000000006</v>
+        <v>106.027</v>
       </c>
       <c r="F84">
-        <v>587.8580000000001</v>
+        <v>595.027</v>
       </c>
       <c r="G84">
         <v>95.40000000000001</v>
@@ -8175,28 +8175,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M84">
-        <v>52.90722</v>
+        <v>53.55243</v>
       </c>
       <c r="N84">
-        <v>31.29277999999999</v>
+        <v>30.64756999999999</v>
       </c>
       <c r="O84">
-        <v>5.945628199999997</v>
+        <v>5.823038299999998</v>
       </c>
       <c r="P84">
-        <v>25.34715179999999</v>
+        <v>24.82453169999999</v>
       </c>
       <c r="Q84">
-        <v>94.1471518</v>
+        <v>93.62453170000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2517357774856099</v>
+        <v>0.2633588929839825</v>
       </c>
       <c r="T84">
-        <v>3.771786086306748</v>
+        <v>3.984667528529003</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.591465210230286</v>
+        <v>1.572290930588957</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.105278011807277</v>
+        <v>0.1054655836671443</v>
       </c>
       <c r="C85">
-        <v>-59.05989084456064</v>
+        <v>-67.61391026415811</v>
       </c>
       <c r="D85">
-        <v>440.5671091554394</v>
+        <v>439.1820897358419</v>
       </c>
       <c r="E85">
-        <v>106.027</v>
+        <v>113.196</v>
       </c>
       <c r="F85">
-        <v>595.027</v>
+        <v>602.196</v>
       </c>
       <c r="G85">
         <v>95.40000000000001</v>
@@ -8257,28 +8257,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M85">
-        <v>53.55243</v>
+        <v>54.19764</v>
       </c>
       <c r="N85">
-        <v>30.64756999999999</v>
+        <v>30.00235999999999</v>
       </c>
       <c r="O85">
-        <v>5.823038299999998</v>
+        <v>5.700448399999998</v>
       </c>
       <c r="P85">
-        <v>24.82453169999999</v>
+        <v>24.30191159999999</v>
       </c>
       <c r="Q85">
-        <v>93.62453170000001</v>
+        <v>93.10191159999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2633588929839825</v>
+        <v>0.2764348979196517</v>
       </c>
       <c r="T85">
-        <v>3.984667528529003</v>
+        <v>4.22415915102904</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.572290930588957</v>
+        <v>1.553573181415279</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1054655836671443</v>
+        <v>0.1056531555270115</v>
       </c>
       <c r="C86">
-        <v>-67.61391026415799</v>
+        <v>-76.15924874901793</v>
       </c>
       <c r="D86">
-        <v>439.1820897358419</v>
+        <v>437.805751250982</v>
       </c>
       <c r="E86">
-        <v>113.1959999999999</v>
+        <v>120.365</v>
       </c>
       <c r="F86">
-        <v>602.1959999999999</v>
+        <v>609.365</v>
       </c>
       <c r="G86">
         <v>95.40000000000001</v>
@@ -8339,28 +8339,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M86">
-        <v>54.19763999999999</v>
+        <v>54.84285</v>
       </c>
       <c r="N86">
-        <v>30.00236</v>
+        <v>29.35714999999999</v>
       </c>
       <c r="O86">
-        <v>5.700448399999999</v>
+        <v>5.577858499999998</v>
       </c>
       <c r="P86">
-        <v>24.3019116</v>
+        <v>23.77929149999999</v>
       </c>
       <c r="Q86">
-        <v>93.10191160000001</v>
+        <v>92.57929150000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2764348979196515</v>
+        <v>0.2912543701800765</v>
       </c>
       <c r="T86">
-        <v>4.224159151029037</v>
+        <v>4.495582989862412</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.553573181415279</v>
+        <v>1.535295849869217</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1056531555270115</v>
+        <v>0.1058407273868787</v>
       </c>
       <c r="C87">
-        <v>-76.15924874901793</v>
+        <v>-84.69598765886781</v>
       </c>
       <c r="D87">
-        <v>437.805751250982</v>
+        <v>436.4380123411322</v>
       </c>
       <c r="E87">
-        <v>120.365</v>
+        <v>127.534</v>
       </c>
       <c r="F87">
-        <v>609.365</v>
+        <v>616.534</v>
       </c>
       <c r="G87">
         <v>95.40000000000001</v>
@@ -8421,28 +8421,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M87">
-        <v>54.84285</v>
+        <v>55.48806</v>
       </c>
       <c r="N87">
-        <v>29.35714999999999</v>
+        <v>28.71193999999999</v>
       </c>
       <c r="O87">
-        <v>5.577858499999998</v>
+        <v>5.455268599999998</v>
       </c>
       <c r="P87">
-        <v>23.77929149999999</v>
+        <v>23.25667139999999</v>
       </c>
       <c r="Q87">
-        <v>92.57929150000001</v>
+        <v>92.0566714</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2912543701800765</v>
+        <v>0.3081909099062766</v>
       </c>
       <c r="T87">
-        <v>4.495582989862412</v>
+        <v>4.805781662814841</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.535295849869217</v>
+        <v>1.517443572545156</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1058407273868787</v>
+        <v>0.106028299246746</v>
       </c>
       <c r="C88">
-        <v>-84.69598765886781</v>
+        <v>-93.22420733990521</v>
       </c>
       <c r="D88">
-        <v>436.4380123411322</v>
+        <v>435.0787926600947</v>
       </c>
       <c r="E88">
-        <v>127.534</v>
+        <v>134.703</v>
       </c>
       <c r="F88">
-        <v>616.534</v>
+        <v>623.703</v>
       </c>
       <c r="G88">
         <v>95.40000000000001</v>
@@ -8503,28 +8503,28 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M88">
-        <v>55.48806</v>
+        <v>56.13327</v>
       </c>
       <c r="N88">
-        <v>28.71193999999999</v>
+        <v>28.06672999999999</v>
       </c>
       <c r="O88">
-        <v>5.455268599999998</v>
+        <v>5.332678699999999</v>
       </c>
       <c r="P88">
-        <v>23.25667139999999</v>
+        <v>22.73405129999999</v>
       </c>
       <c r="Q88">
-        <v>92.0566714</v>
+        <v>91.5340513</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3081909099062766</v>
+        <v>0.3277330711288151</v>
       </c>
       <c r="T88">
-        <v>4.805781662814841</v>
+        <v>5.163703208529181</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.517443572545156</v>
+        <v>1.500001692400959</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.106028299246746</v>
+        <v>0.1495991952072643</v>
       </c>
       <c r="C89">
-        <v>-93.22420733990521</v>
+        <v>-283.0224923913779</v>
       </c>
       <c r="D89">
-        <v>435.0787926600947</v>
+        <v>252.4495076086221</v>
       </c>
       <c r="E89">
-        <v>134.703</v>
+        <v>141.872</v>
       </c>
       <c r="F89">
-        <v>623.703</v>
+        <v>630.872</v>
       </c>
       <c r="G89">
         <v>95.40000000000001</v>
@@ -8585,45 +8585,45 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M89">
-        <v>56.13327</v>
+        <v>92.61200960000001</v>
       </c>
       <c r="N89">
-        <v>28.06672999999999</v>
+        <v>-8.412009600000019</v>
       </c>
       <c r="O89">
-        <v>5.332678699999999</v>
+        <v>-1.598281824000004</v>
       </c>
       <c r="P89">
-        <v>22.73405129999999</v>
+        <v>-6.813727776000015</v>
       </c>
       <c r="Q89">
-        <v>91.5340513</v>
+        <v>61.986272224</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3277330711288151</v>
+        <v>0.3560893365426115</v>
       </c>
       <c r="T89">
-        <v>5.163703208529181</v>
+        <v>5.683058167891947</v>
       </c>
       <c r="U89">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.19</v>
+        <v>0.172742175330142</v>
       </c>
       <c r="W89">
-        <v>0.07290000000000001</v>
+        <v>0.1214414486615352</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.500001692400959</v>
+        <v>0.9091693438428528</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1495991952072643</v>
+        <v>0.1506091952072643</v>
       </c>
       <c r="C90">
-        <v>-283.0224923913779</v>
+        <v>-292.6242369819691</v>
       </c>
       <c r="D90">
-        <v>252.4495076086221</v>
+        <v>250.0167630180308</v>
       </c>
       <c r="E90">
-        <v>141.872</v>
+        <v>149.0409999999999</v>
       </c>
       <c r="F90">
-        <v>630.872</v>
+        <v>638.0409999999999</v>
       </c>
       <c r="G90">
         <v>95.40000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M90">
-        <v>92.61200960000001</v>
+        <v>93.66441880000001</v>
       </c>
       <c r="N90">
-        <v>-8.412009600000019</v>
+        <v>-9.464418800000018</v>
       </c>
       <c r="O90">
-        <v>-1.598281824000004</v>
+        <v>-1.798239572000004</v>
       </c>
       <c r="P90">
-        <v>-6.813727776000015</v>
+        <v>-7.666179228000015</v>
       </c>
       <c r="Q90">
-        <v>61.986272224</v>
+        <v>61.13382077199999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3560893365426115</v>
+        <v>0.3842974580464853</v>
       </c>
       <c r="T90">
-        <v>5.683058167891947</v>
+        <v>6.199699819518488</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.172742175330142</v>
+        <v>0.1708012520118258</v>
       </c>
       <c r="W90">
-        <v>0.1214414486615352</v>
+        <v>0.121726376204664</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9091693438428528</v>
+        <v>0.8989539579569781</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1506091952072643</v>
+        <v>0.1516191952072643</v>
       </c>
       <c r="C91">
-        <v>-292.6242369819691</v>
+        <v>-302.1795425114492</v>
       </c>
       <c r="D91">
-        <v>250.0167630180308</v>
+        <v>247.6304574885508</v>
       </c>
       <c r="E91">
-        <v>149.0409999999999</v>
+        <v>156.21</v>
       </c>
       <c r="F91">
-        <v>638.0409999999999</v>
+        <v>645.21</v>
       </c>
       <c r="G91">
         <v>95.40000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M91">
-        <v>93.66441880000001</v>
+        <v>94.71682800000002</v>
       </c>
       <c r="N91">
-        <v>-9.464418800000018</v>
+        <v>-10.51682800000003</v>
       </c>
       <c r="O91">
-        <v>-1.798239572000004</v>
+        <v>-1.998197320000006</v>
       </c>
       <c r="P91">
-        <v>-7.666179228000015</v>
+        <v>-8.518630680000026</v>
       </c>
       <c r="Q91">
-        <v>61.13382077199999</v>
+        <v>60.28136931999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3842974580464853</v>
+        <v>0.4181472038511339</v>
       </c>
       <c r="T91">
-        <v>6.199699819518488</v>
+        <v>6.819669801470337</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1708012520118258</v>
+        <v>0.1689034603228055</v>
       </c>
       <c r="W91">
-        <v>0.121726376204664</v>
+        <v>0.1220049720246122</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8989539579569781</v>
+        <v>0.8889655806463448</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1516191952072643</v>
+        <v>0.1526291952072643</v>
       </c>
       <c r="C92">
-        <v>-302.1795425114492</v>
+        <v>-311.6897261324452</v>
       </c>
       <c r="D92">
-        <v>247.6304574885508</v>
+        <v>245.2892738675548</v>
       </c>
       <c r="E92">
-        <v>156.21</v>
+        <v>163.379</v>
       </c>
       <c r="F92">
-        <v>645.21</v>
+        <v>652.379</v>
       </c>
       <c r="G92">
         <v>95.40000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M92">
-        <v>94.71682800000002</v>
+        <v>95.76923720000001</v>
       </c>
       <c r="N92">
-        <v>-10.51682800000003</v>
+        <v>-11.56923720000002</v>
       </c>
       <c r="O92">
-        <v>-1.998197320000006</v>
+        <v>-2.198155068000003</v>
       </c>
       <c r="P92">
-        <v>-8.518630680000026</v>
+        <v>-9.371082132000014</v>
       </c>
       <c r="Q92">
-        <v>60.28136931999998</v>
+        <v>59.428917868</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4181472038511339</v>
+        <v>0.4595191153901488</v>
       </c>
       <c r="T92">
-        <v>6.819669801470337</v>
+        <v>7.577410890522597</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1689034603228055</v>
+        <v>0.1670473783412363</v>
       </c>
       <c r="W92">
-        <v>0.1220049720246122</v>
+        <v>0.1222774448595065</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8889655806463448</v>
+        <v>0.8791967281117697</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1526291952072643</v>
+        <v>0.1536391952072643</v>
       </c>
       <c r="C93">
-        <v>-311.6897261324452</v>
+        <v>-321.1560556528489</v>
       </c>
       <c r="D93">
-        <v>245.2892738675548</v>
+        <v>242.9919443471511</v>
       </c>
       <c r="E93">
-        <v>163.379</v>
+        <v>170.548</v>
       </c>
       <c r="F93">
-        <v>652.379</v>
+        <v>659.548</v>
       </c>
       <c r="G93">
         <v>95.40000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M93">
-        <v>95.76923720000001</v>
+        <v>96.82164640000001</v>
       </c>
       <c r="N93">
-        <v>-11.56923720000002</v>
+        <v>-12.62164640000002</v>
       </c>
       <c r="O93">
-        <v>-2.198155068000003</v>
+        <v>-2.398112816000003</v>
       </c>
       <c r="P93">
-        <v>-9.371082132000014</v>
+        <v>-10.22353358400001</v>
       </c>
       <c r="Q93">
-        <v>59.428917868</v>
+        <v>58.576466416</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4595191153901488</v>
+        <v>0.5112340048139176</v>
       </c>
       <c r="T93">
-        <v>7.577410890522597</v>
+        <v>8.524587251837925</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1670473783412363</v>
+        <v>0.1652316459679619</v>
       </c>
       <c r="W93">
-        <v>0.1222774448595065</v>
+        <v>0.1225439943719032</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8791967281117697</v>
+        <v>0.8696402419366418</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1536391952072643</v>
+        <v>0.1546491952072643</v>
       </c>
       <c r="C94">
-        <v>-321.1560556528489</v>
+        <v>-330.5797518251386</v>
       </c>
       <c r="D94">
-        <v>242.9919443471511</v>
+        <v>240.7372481748614</v>
       </c>
       <c r="E94">
-        <v>170.548</v>
+        <v>177.717</v>
       </c>
       <c r="F94">
-        <v>659.548</v>
+        <v>666.717</v>
       </c>
       <c r="G94">
         <v>95.40000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M94">
-        <v>96.82164640000001</v>
+        <v>97.87405560000001</v>
       </c>
       <c r="N94">
-        <v>-12.62164640000002</v>
+        <v>-13.67405560000002</v>
       </c>
       <c r="O94">
-        <v>-2.398112816000003</v>
+        <v>-2.598070564000003</v>
       </c>
       <c r="P94">
-        <v>-10.22353358400001</v>
+        <v>-11.07598503600001</v>
       </c>
       <c r="Q94">
-        <v>58.576466416</v>
+        <v>57.724014964</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5112340048139176</v>
+        <v>0.5777245769301914</v>
       </c>
       <c r="T94">
-        <v>8.524587251837925</v>
+        <v>9.742385430671915</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1652316459679619</v>
+        <v>0.1634549616027151</v>
       </c>
       <c r="W94">
-        <v>0.1225439943719032</v>
+        <v>0.1228048116367215</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8696402419366418</v>
+        <v>0.8602892715932371</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1546491952072643</v>
+        <v>0.1556591952072643</v>
       </c>
       <c r="C95">
-        <v>-330.5797518251386</v>
+        <v>-339.9619905094187</v>
       </c>
       <c r="D95">
-        <v>240.7372481748614</v>
+        <v>238.5240094905813</v>
       </c>
       <c r="E95">
-        <v>177.717</v>
+        <v>184.886</v>
       </c>
       <c r="F95">
-        <v>666.717</v>
+        <v>673.886</v>
       </c>
       <c r="G95">
         <v>95.40000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M95">
-        <v>97.87405560000001</v>
+        <v>98.92646480000001</v>
       </c>
       <c r="N95">
-        <v>-13.67405560000002</v>
+        <v>-14.72646480000002</v>
       </c>
       <c r="O95">
-        <v>-2.598070564000003</v>
+        <v>-2.798028312000003</v>
       </c>
       <c r="P95">
-        <v>-11.07598503600001</v>
+        <v>-11.92843648800001</v>
       </c>
       <c r="Q95">
-        <v>57.724014964</v>
+        <v>56.87156351199999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5777245769301914</v>
+        <v>0.6663786730852235</v>
       </c>
       <c r="T95">
-        <v>9.742385430671915</v>
+        <v>11.3661163357839</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1634549616027151</v>
+        <v>0.1617160790324734</v>
       </c>
       <c r="W95">
-        <v>0.1228048116367215</v>
+        <v>0.1230600795980329</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8602892715932371</v>
+        <v>0.8511372580656494</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1556591952072643</v>
+        <v>0.1566691952072643</v>
       </c>
       <c r="C96">
-        <v>-339.9619905094187</v>
+        <v>-349.3039047182315</v>
       </c>
       <c r="D96">
-        <v>238.5240094905813</v>
+        <v>236.3510952817686</v>
       </c>
       <c r="E96">
-        <v>184.886</v>
+        <v>192.0550000000001</v>
       </c>
       <c r="F96">
-        <v>673.886</v>
+        <v>681.0550000000001</v>
       </c>
       <c r="G96">
         <v>95.40000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M96">
-        <v>98.92646480000001</v>
+        <v>99.97887400000002</v>
       </c>
       <c r="N96">
-        <v>-14.72646480000002</v>
+        <v>-15.77887400000003</v>
       </c>
       <c r="O96">
-        <v>-2.798028312000003</v>
+        <v>-2.997986060000006</v>
       </c>
       <c r="P96">
-        <v>-11.92843648800001</v>
+        <v>-12.78088794000002</v>
       </c>
       <c r="Q96">
-        <v>56.87156351199999</v>
+        <v>56.01911205999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6663786730852235</v>
+        <v>0.7904944077022685</v>
       </c>
       <c r="T96">
-        <v>11.3661163357839</v>
+        <v>13.63933960294069</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1617160790324734</v>
+        <v>0.1600138045163421</v>
       </c>
       <c r="W96">
-        <v>0.1230600795980329</v>
+        <v>0.123309973497001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8511372580656494</v>
+        <v>0.8421779185070635</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1566691952072643</v>
+        <v>0.1576791952072643</v>
       </c>
       <c r="C97">
-        <v>-349.3039047182315</v>
+        <v>-358.6065865506074</v>
       </c>
       <c r="D97">
-        <v>236.3510952817686</v>
+        <v>234.2174134493926</v>
       </c>
       <c r="E97">
-        <v>192.0550000000001</v>
+        <v>199.224</v>
       </c>
       <c r="F97">
-        <v>681.0550000000001</v>
+        <v>688.224</v>
       </c>
       <c r="G97">
         <v>95.40000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M97">
-        <v>99.97887400000002</v>
+        <v>101.0312832</v>
       </c>
       <c r="N97">
-        <v>-15.77887400000003</v>
+        <v>-16.83128320000003</v>
       </c>
       <c r="O97">
-        <v>-2.997986060000006</v>
+        <v>-3.197943808000006</v>
       </c>
       <c r="P97">
-        <v>-12.78088794000002</v>
+        <v>-13.63333939200002</v>
       </c>
       <c r="Q97">
-        <v>56.01911205999998</v>
+        <v>55.16666060799999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7904944077022685</v>
+        <v>0.9766680096278362</v>
       </c>
       <c r="T97">
-        <v>13.63933960294069</v>
+        <v>17.04917450367587</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1600138045163421</v>
+        <v>0.1583469940526302</v>
       </c>
       <c r="W97">
-        <v>0.123309973497001</v>
+        <v>0.1235546612730739</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8421779185070635</v>
+        <v>0.8334052318559483</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1576791952072643</v>
+        <v>0.1586891952072643</v>
       </c>
       <c r="C98">
-        <v>-358.6065865506073</v>
+        <v>-367.871089022297</v>
       </c>
       <c r="D98">
-        <v>234.2174134493926</v>
+        <v>232.1219109777029</v>
       </c>
       <c r="E98">
-        <v>199.2239999999999</v>
+        <v>206.3929999999999</v>
       </c>
       <c r="F98">
-        <v>688.2239999999999</v>
+        <v>695.3929999999999</v>
       </c>
       <c r="G98">
         <v>95.40000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M98">
-        <v>101.0312832</v>
+        <v>102.0836924</v>
       </c>
       <c r="N98">
-        <v>-16.83128320000002</v>
+        <v>-17.88369240000002</v>
       </c>
       <c r="O98">
-        <v>-3.197943808000003</v>
+        <v>-3.397901556000003</v>
       </c>
       <c r="P98">
-        <v>-13.63333939200001</v>
+        <v>-14.48579084400001</v>
       </c>
       <c r="Q98">
-        <v>55.166660608</v>
+        <v>54.314209156</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9766680096278336</v>
+        <v>1.286957346170445</v>
       </c>
       <c r="T98">
-        <v>17.04917450367583</v>
+        <v>22.73223267156777</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1583469940526302</v>
+        <v>0.1567145508149742</v>
       </c>
       <c r="W98">
-        <v>0.1235546612730739</v>
+        <v>0.1237943039403618</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8334052318559484</v>
+        <v>0.8248134253419696</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1586891952072643</v>
+        <v>0.1596991952072643</v>
       </c>
       <c r="C99">
-        <v>-367.871089022297</v>
+        <v>-377.0984277986235</v>
       </c>
       <c r="D99">
-        <v>232.1219109777029</v>
+        <v>230.0635722013765</v>
       </c>
       <c r="E99">
-        <v>206.3929999999999</v>
+        <v>213.562</v>
       </c>
       <c r="F99">
-        <v>695.3929999999999</v>
+        <v>702.562</v>
       </c>
       <c r="G99">
         <v>95.40000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M99">
-        <v>102.0836924</v>
+        <v>103.1361016</v>
       </c>
       <c r="N99">
-        <v>-17.88369240000002</v>
+        <v>-18.93610160000003</v>
       </c>
       <c r="O99">
-        <v>-3.397901556000003</v>
+        <v>-3.597859304000006</v>
       </c>
       <c r="P99">
-        <v>-14.48579084400001</v>
+        <v>-15.33824229600002</v>
       </c>
       <c r="Q99">
-        <v>54.314209156</v>
+        <v>53.46175770399999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.286957346170445</v>
+        <v>1.907536019255667</v>
       </c>
       <c r="T99">
-        <v>22.73223267156777</v>
+        <v>34.09834900735165</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1567145508149742</v>
+        <v>0.1551154227454336</v>
       </c>
       <c r="W99">
-        <v>0.1237943039403618</v>
+        <v>0.1240290559409704</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8248134253419696</v>
+        <v>0.8163969618180718</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1596991952072643</v>
+        <v>0.1607091952072643</v>
       </c>
       <c r="C100">
-        <v>-377.0984277986235</v>
+        <v>-386.289582835949</v>
       </c>
       <c r="D100">
-        <v>230.0635722013765</v>
+        <v>228.041417164051</v>
       </c>
       <c r="E100">
-        <v>213.562</v>
+        <v>220.731</v>
       </c>
       <c r="F100">
-        <v>702.562</v>
+        <v>709.731</v>
       </c>
       <c r="G100">
         <v>95.40000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>84.19999999999999</v>
       </c>
       <c r="M100">
-        <v>103.1361016</v>
+        <v>104.1885108</v>
       </c>
       <c r="N100">
-        <v>-18.93610160000003</v>
+        <v>-19.98851080000001</v>
       </c>
       <c r="O100">
-        <v>-3.597859304000006</v>
+        <v>-3.797817052000003</v>
       </c>
       <c r="P100">
-        <v>-15.33824229600002</v>
+        <v>-16.19069374800001</v>
       </c>
       <c r="Q100">
-        <v>53.46175770399999</v>
+        <v>52.609306252</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.907536019255667</v>
+        <v>3.769272038511334</v>
       </c>
       <c r="T100">
-        <v>34.09834900735165</v>
+        <v>68.19669801470329</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1551154227454336</v>
+        <v>0.1535486002934596</v>
       </c>
       <c r="W100">
-        <v>0.1240290559409704</v>
+        <v>0.1242590654769201</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8163969618180718</v>
+        <v>0.8081505278603136</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1607091952072643</v>
-      </c>
-      <c r="C101">
-        <v>-386.289582835949</v>
-      </c>
-      <c r="D101">
-        <v>228.041417164051</v>
-      </c>
-      <c r="E101">
-        <v>220.731</v>
-      </c>
-      <c r="F101">
-        <v>709.731</v>
-      </c>
-      <c r="G101">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>227.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>153</v>
-      </c>
-      <c r="K101">
-        <v>68.80000000000001</v>
-      </c>
-      <c r="L101">
-        <v>84.19999999999999</v>
-      </c>
-      <c r="M101">
-        <v>104.1885108</v>
-      </c>
-      <c r="N101">
-        <v>-19.98851080000001</v>
-      </c>
-      <c r="O101">
-        <v>-3.797817052000003</v>
-      </c>
-      <c r="P101">
-        <v>-16.19069374800001</v>
-      </c>
-      <c r="Q101">
-        <v>52.609306252</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.769272038511334</v>
-      </c>
-      <c r="T101">
-        <v>68.19669801470329</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1535486002934596</v>
-      </c>
-      <c r="W101">
-        <v>0.1242590654769201</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8081505278603136</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
